--- a/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>FBHS</t>
   </si>
@@ -656,415 +656,427 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1161300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1261200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1163700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1040000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4723000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1195500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1255400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1140200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4801100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1986300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1936100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1771000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1659700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1652100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1375800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1402700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1470500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1459000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1507200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1327900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1420700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1380800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1429000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1254600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1382500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1348600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1365400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1186800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1301600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1279000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>666400</v>
+      </c>
+      <c r="E9" s="3">
         <v>721100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>695600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>631700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2790100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>716600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>742000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>671800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2840600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1280000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1230300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1126900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1052000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1071500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>892900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>909500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>934600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>934800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>969600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>869100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>920300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>880800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>898900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>814600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>885700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>843200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>850500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>768500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>826400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>798200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>494900</v>
+      </c>
+      <c r="E10" s="3">
         <v>540100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>468100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>408300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1932900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>478900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>513400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>468400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1960500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>706300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>705800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>644100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>607700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>580600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>482900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>493200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>535900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>524200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>537600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>458800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>500400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>500000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>530100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>440000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>496800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>505400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>514900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>418300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>475200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>480800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1097,8 +1109,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1189,8 +1202,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,192 +1297,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E14" s="3">
         <v>3700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>22200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>32400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>20600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>27000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>23400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>14000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>23000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>35000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>43400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>38400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>16300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>18100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E15" s="3">
         <v>18800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>12600</v>
       </c>
       <c r="F15" s="3">
         <v>12600</v>
       </c>
       <c r="G15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="H15" s="3">
         <v>48300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>12500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>11600</v>
       </c>
       <c r="J15" s="3">
         <v>11600</v>
       </c>
       <c r="K15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="L15" s="3">
         <v>46400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>15900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>10900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>10500</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>10300</v>
       </c>
       <c r="R15" s="3">
         <v>10300</v>
       </c>
       <c r="S15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="T15" s="3">
         <v>11400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>9900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>10100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>10000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>10800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>8900</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>8200</v>
       </c>
       <c r="Z15" s="3">
         <v>8200</v>
       </c>
       <c r="AA15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AB15" s="3">
         <v>8100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>7500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>8000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>8100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>7700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,192 +1521,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1027400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1064700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1011100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>908200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3948700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1002800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1035900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>960400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3990000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1699700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1641200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1522600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1426500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1411900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1202800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1247700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1278000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1291000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1304800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1192300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1280600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1233700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1240400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1219700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1156200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1071900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1095900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E18" s="3">
         <v>196500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>152600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>131800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>774300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>192700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>219500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>179800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>811100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>286600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>294900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>248400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>233200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>240200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>173000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>155000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>192500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>168000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>202400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>135600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>140100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>147100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>188600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>119400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>162800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>199500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>209200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>114900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>166400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>183100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,468 +1746,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>9400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>12000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1300</v>
       </c>
       <c r="M20" s="3">
         <v>1300</v>
       </c>
       <c r="N20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O20" s="3">
         <v>-3300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-31200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>9600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>189800</v>
+      </c>
+      <c r="E21" s="3">
         <v>251300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>192000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>170000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>977900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>244100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>266600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>228800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>999800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>334100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>343700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>292800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>279700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>281600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>218300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>198600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>201300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>205000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>241300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>174600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>181300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>194200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>229900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>155700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>189300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>234000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>243700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>147500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>197800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>212400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E22" s="3">
         <v>33300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>26800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>119200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>30500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>21700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>84300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>22200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>22100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>22400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>24500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>14700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12900</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>12300</v>
       </c>
       <c r="AC22" s="3">
         <v>12300</v>
       </c>
       <c r="AD22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AE22" s="3">
         <v>11900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>103900</v>
+      </c>
+      <c r="E23" s="3">
         <v>172600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>130100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>111300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>667100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>162500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>189200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>160200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>726400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>267300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>275000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>223700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>213600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>222200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>156000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>139000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>138900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>144700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>178600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>113100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>117200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>137700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>174600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>107500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>142400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>189400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>199200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>103800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>153200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E24" s="3">
         <v>36100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>25700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>127200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>44900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>34000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>166700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>65200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>57800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>45900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>47100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>54000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>37800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>29900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>34900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>39000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>41500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>28600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>28700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>40900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>44900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>27000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>40100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>59800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>58900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>26400</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>48800</v>
       </c>
       <c r="AF24" s="3">
         <v>48800</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>48800</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,192 +2314,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E26" s="3">
         <v>136500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>102100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>85600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>539900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>141400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>144300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>126200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>559700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>202100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>217200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>177800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>166500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>168200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>118200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>109100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>104000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>105700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>137100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>84500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>88500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>96800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>129700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>80500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>102300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>129600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>140300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>77400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>104400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E27" s="3">
         <v>136500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>102100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>85600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>539900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>141400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>144300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>126200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>559700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>202100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>217200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>177800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>163600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>164600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>115800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>109100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>104100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>105600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>137500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>84700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>88400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>96700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>129600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>80600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>102300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>129500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>140300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>77400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>104300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2599,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2554,31 +2614,31 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>-1000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>146800</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>62800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>47700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>54700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>212700</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2586,14 +2646,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2605,37 +2665,40 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-3200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>3100</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>25700</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-700</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2789,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,192 +2884,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-12000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1300</v>
       </c>
       <c r="M32" s="3">
         <v>-1300</v>
       </c>
       <c r="N32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="O32" s="3">
         <v>3300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>31200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E33" s="3">
         <v>136500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>102100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>84600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>686700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>204200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>192000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>180900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>772400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>202100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>217200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>177800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>163600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>164600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>115800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>109100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>104100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>105600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>137500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>84700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>85200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>99800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>129600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>75000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>128000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>129500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>137700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>77400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>103600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,197 +3169,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E35" s="3">
         <v>136500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>102100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>84600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>686700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>204200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>192000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>180900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>772400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>202100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>217200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>177800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>163600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>164600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>115800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>109100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>104100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>105600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>137500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>84700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>85200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>99800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>129600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>75000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>128000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>129500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>137700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>77400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>103600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3401,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,100 +3436,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>366400</v>
+      </c>
+      <c r="E41" s="3">
         <v>453400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>681700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>539100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>642500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>345300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>360600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>378200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>471500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>460700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>460000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>356100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>419100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>464500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>398400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>359700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>387900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>336200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>276300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>281200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>262900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>389900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>345500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>244400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>323000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>277100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>252700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>210800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>251500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>278600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3535,376 +3624,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>534200</v>
+      </c>
+      <c r="E43" s="3">
         <v>578600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>621200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>559000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>521800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>936100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>998500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1011600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>885700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>921800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>844600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>828500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>734900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>765200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>657700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>678200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>624800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>640100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>706200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>650100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>571700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>635400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>657500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>631500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>555300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>594700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>595700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>564900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>550700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>568800</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>982300</v>
+      </c>
+      <c r="E44" s="3">
         <v>930000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>954500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>931100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1021300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1502300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1446700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1334700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1193800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1128300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1046800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>958400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>867200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>738300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>732300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>703100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>718600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>758800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>741900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>737900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>678900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>684300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>627000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>619200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>580800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>600100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>581400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>558800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>531100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>562500</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>162800</v>
+      </c>
+      <c r="E45" s="3">
         <v>187700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>186200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>272000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>274800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>223900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>258000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>232200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>193500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>215200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>197500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>202900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>187300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>170000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>168900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>173000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>166900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>171600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>192500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>178800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>172600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>180600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>175500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>149400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>142600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>126400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>123300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>121600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>111900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>129800</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2045700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2149700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2443600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2301200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2460400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3007600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3063800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2956700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2744500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2726000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2548900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2345900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2208500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2138000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1957300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1914000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1898200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1906700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1916900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1848000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1686100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1890200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1805500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1644500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1601700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1598300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1553100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1456100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1445200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1539700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3995,192 +4099,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1148800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1052400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>980700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>917700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>902600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1274700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1266800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1248300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1201200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1134100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1107400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1084300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1087600</v>
-      </c>
-      <c r="P48" s="3">
-        <v>958600</v>
       </c>
       <c r="Q48" s="3">
         <v>958600</v>
       </c>
       <c r="R48" s="3">
+        <v>958600</v>
+      </c>
+      <c r="S48" s="3">
         <v>966900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>989800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>966200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>978100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>981100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>813400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>776300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>737600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>742800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>740000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>690600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>675600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>665700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>662500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>642900</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3261500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3304200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3332200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2634300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2641500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3922100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3814200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3870000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3848900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3867900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3891200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3900500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3815100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3196400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3199300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3219200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3259100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3271000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3314900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3323700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3327100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3397100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3055700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3069900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3074400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2958200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2925300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2930100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2940800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2948900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4384,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,100 +4479,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E52" s="3">
         <v>111800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>116700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>119500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>116400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>211200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>189300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>168000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>141600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>140800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>148500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>151400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>247500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>226000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>217100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>200000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>144200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>141700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>133500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>136400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>138000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>106100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>98300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>94800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>95300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>102200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>99400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>82200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>80000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,100 +4669,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6565000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6618100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6873200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5972700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6120900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8415600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8334100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8243000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7936200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7868800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7696000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7482100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7358700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6519000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6332300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6300100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6291300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6285600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6343400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6289200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5964600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6169700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5697100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5552000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5511400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5349300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5253400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5134100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5128500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5212600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4801,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,100 +4836,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>568100</v>
+      </c>
+      <c r="E57" s="3">
         <v>570400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>489500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>423700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>421600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>672600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>756300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>728100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>764900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>735700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>697500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>599200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>620500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>544100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>463900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>426400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>460000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>436500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>476600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>442000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>459000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>437700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>428700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>417100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>428800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>392500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>397000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>378900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>393800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>361900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4808,28 +4941,28 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>599800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>599500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>599200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>600300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>400000</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -4837,8 +4970,8 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4847,34 +4980,34 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>399900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>399700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>399500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>749300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>350000</v>
-      </c>
-      <c r="W58" s="3">
-        <v>525000</v>
       </c>
       <c r="X58" s="3">
         <v>525000</v>
       </c>
       <c r="Y58" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="Z58" s="3">
         <v>350000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
+      <c r="AA58" s="3">
+        <v>350000</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>8</v>
@@ -4885,382 +5018,397 @@
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>632300</v>
+      </c>
+      <c r="E59" s="3">
         <v>621700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>551400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>390000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>523900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>775000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>685200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>626700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>806200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>793100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>667200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>597800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>724600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>590900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>488900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>419800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>549600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>540600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>469300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>446800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>508100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>488900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>451800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>373700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>478000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>460000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>394100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>328900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>449000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1192100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1640700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1413200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1544700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2047900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1441500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1354800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1971100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1528800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1364700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1197000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1345100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1135000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>952800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1246100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1409300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1376600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1695200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1238800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1492100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1451600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1230500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1140800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>906800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>852500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>791100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>707800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>842800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>776700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2670100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2829300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2668500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2074900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2074300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2786900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3357900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3367900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2309800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2629100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2608300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2682800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2572200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2086500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2245900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2035200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1784600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1949000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1666000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2169700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1809000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1988400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1793300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1538000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1507600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1462200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1391900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1491500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1431100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1585800</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>401100</v>
+      </c>
+      <c r="E62" s="3">
         <v>377700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>386900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>402100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>415000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>550700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>582300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>605500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>590500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>656300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>679500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>677900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>665900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>668900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>670500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>660900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>669600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>623300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>637500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>633600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>483500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>496100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>498600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>514900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>495900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>488700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>501700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>504100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>491600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>489900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5499,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5594,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,100 +5689,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4271600</v>
+      </c>
+      <c r="E66" s="3">
         <v>4399100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4696100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3890200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4034000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5385500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5381700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5328200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4871400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4814200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4652500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4557700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4583200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3890400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3870500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3943100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3864700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3950200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3999900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4043700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3786400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3937800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3524000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3195200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2911900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2805000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2686200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2704900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2767000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2853800</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5821,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5914,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6009,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5937,8 +6104,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,100 +6199,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2605300</v>
+      </c>
+      <c r="E72" s="3">
         <v>2554200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2475400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2402400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2323800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3277000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3145000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2989400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2807900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2670000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2539300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2358000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2180200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2052700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1954700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1872100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1763000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1692500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1648100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1541400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1448100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1393400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1350500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1249900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1076500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1002000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>892000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>814600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6389,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6484,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,100 +6579,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2293400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2219000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2177100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2082500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2086900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3030100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2952400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2914800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3064800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3054600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3043500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2924400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2775500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2628600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2461800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2357000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2426600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2335400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2343500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2245500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2178200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2231900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2173100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2356800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2599500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2544300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2567200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2429200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2361500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2358800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,197 +6769,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E81" s="3">
         <v>136500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>102100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>84600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>686700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>204200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>192000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>180900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>772400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>202100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>217200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>177800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>163600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>164600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>115800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>109100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>104100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>105600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>137500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>84700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>85200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>99800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>129600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>75000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>128000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>129500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>137700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>77400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>103600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,100 +7001,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E83" s="3">
         <v>45400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>34200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>31900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>191600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>48600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>46900</v>
       </c>
       <c r="J83" s="3">
         <v>46900</v>
       </c>
       <c r="K83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="L83" s="3">
         <v>189100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>46200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>47500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>47700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>46600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>39300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>40100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>37500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>40000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>36700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>38200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>37800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>40700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>37500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>37900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>33500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>34000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>32300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>32200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>31800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>33000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7189,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7284,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7379,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7474,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,100 +7569,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>220200</v>
+      </c>
+      <c r="E89" s="3">
         <v>332000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>427500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>76100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>566300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>246900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>225000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-183100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>688700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>168100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>331900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-69200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>318900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>246300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>274300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-13800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>283400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>241800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>201700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-89700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>260300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>206400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>189200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-51900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>247700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>181400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>189100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>269900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,100 +7701,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-80800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-63500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-69600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-42600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-71000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-54800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-60800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-101200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-47200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-84300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-49400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-27500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-43600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-39300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-29600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7889,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,100 +7984,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-80800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-65700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-848700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-455500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-211800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-54800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-114400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-207100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-47200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-40400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-799400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-77000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-49500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-27300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-25500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-25300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-65900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-496100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-29600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-42700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-174500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-50800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-178700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,100 +8116,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-29200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-29100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-29500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-145600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-36200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-36400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-37200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-143000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-35900</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-36000</v>
       </c>
       <c r="N96" s="3">
         <v>-36000</v>
       </c>
       <c r="O96" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-33400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-33300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-33100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-33500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-30700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-30600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-30700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-31000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-28100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-29000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-27400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-27700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-24500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8304,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8399,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,280 +8494,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-210700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-488400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>567100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-139300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>72500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-36000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-176100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>203200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-428600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-115700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-192200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>22800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>420400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-166600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-219500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>77300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-187800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-148900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-182400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>129400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-314200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>342600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-51400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>16200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-108300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>6000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-11100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-14700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>14400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>9900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>7000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-15000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>5500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-7400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-227700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>141600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-103600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>172200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-93600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>51100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>103500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-63200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-45700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>65700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>38600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-28500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>51600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>59500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-5100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-127200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>52400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>101100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>45900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>24400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>41900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-40700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-27100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>FBHS</t>
   </si>
@@ -656,427 +656,440 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1109600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1161300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1261200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1163700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1040000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4723000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1195500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1255400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1140200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4801100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1986300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1936100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1771000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1659700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1652100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1375800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1402700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1470500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1459000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1507200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1327900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1420700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1380800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1429000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1254600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1382500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1348600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1365400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1186800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1301600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1279000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>622000</v>
+      </c>
+      <c r="E9" s="3">
         <v>666400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>721100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>695600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>631700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2790100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>716600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>742000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>671800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2840600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1280000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1230300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1126900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1052000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1071500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>892900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>909500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>934600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>934800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>969600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>869100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>920300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>880800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>898900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>814600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>885700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>843200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>850500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>768500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>826400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>798200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>487600</v>
+      </c>
+      <c r="E10" s="3">
         <v>494900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>540100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>468100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>408300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1932900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>478900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>513400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>468400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1960500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>706300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>705800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>644100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>607700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>580600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>482900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>493200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>535900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>524200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>537600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>458800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>500400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>500000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>530100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>440000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>496800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>505400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>514900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>418300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>475200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>480800</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1110,8 +1123,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1205,8 +1219,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1300,198 +1317,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E14" s="3">
         <v>37100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>22200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>32400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>20600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>27000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>23400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>14000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>23000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>35000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>43400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>38400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>16300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>18100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>6100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E15" s="3">
         <v>18100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18800</v>
-      </c>
-      <c r="F15" s="3">
-        <v>12600</v>
       </c>
       <c r="G15" s="3">
         <v>12600</v>
       </c>
       <c r="H15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="I15" s="3">
         <v>48300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>12500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>11600</v>
       </c>
       <c r="K15" s="3">
         <v>11600</v>
       </c>
       <c r="L15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="M15" s="3">
         <v>46400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>15900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>10900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10500</v>
-      </c>
-      <c r="R15" s="3">
-        <v>10300</v>
       </c>
       <c r="S15" s="3">
         <v>10300</v>
       </c>
       <c r="T15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="U15" s="3">
         <v>11400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>9900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>10100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>10000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>8900</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>8200</v>
       </c>
       <c r="AA15" s="3">
         <v>8200</v>
       </c>
       <c r="AB15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AC15" s="3">
         <v>8100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>7500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>8000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>8100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>7700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1522,198 +1548,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>954200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1027400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1064700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1011100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>908200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3948700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1002800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1035900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>960400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3990000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1699700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1641200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1522600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1426500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1411900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1202800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1247700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1278000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1291000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1304800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1192300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1280600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1233700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1240400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1219700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1156200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1071900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1095900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>155400</v>
+      </c>
+      <c r="E18" s="3">
         <v>133900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>196500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>152600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>131800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>774300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>192700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>219500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>179800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>811100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>286600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>294900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>248400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>233200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>240200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>173000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>155000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>192500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>168000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>202400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>135600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>140100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>147100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>188600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>119400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>162800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>199500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>209200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>114900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>166400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>183100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1747,483 +1780,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>12000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>1300</v>
       </c>
       <c r="N20" s="3">
         <v>1300</v>
       </c>
       <c r="O20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P20" s="3">
         <v>-3300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-31200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>9600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E21" s="3">
         <v>189800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>251300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>192000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>170000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>977900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>244100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>266600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>228800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>999800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>334100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>343700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>292800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>279700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>281600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>218300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>198600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>201300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>205000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>241300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>174600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>181300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>194200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>229900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>155700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>189300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>234000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>243700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>147500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>197800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>212400</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E22" s="3">
         <v>28600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>33300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>26800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>119200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>21700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>84300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>22200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>22100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>22400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>24500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>19000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>14700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12900</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>12300</v>
       </c>
       <c r="AD22" s="3">
         <v>12300</v>
       </c>
       <c r="AE22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AF22" s="3">
         <v>11900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>125200</v>
+      </c>
+      <c r="E23" s="3">
         <v>103900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>172600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>130100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>111300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>667100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>162500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>189200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>160200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>726400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>267300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>275000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>223700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>213600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>222200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>156000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>139000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>138900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>144700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>178600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>113100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>117200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>137700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>174600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>107500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>142400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>189400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>199200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>103800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>153200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E24" s="3">
         <v>22600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>36100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>28000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>25700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>127200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>44900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>34000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>166700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>65200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>57800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>45900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>47100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>54000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>37800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>29900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>34900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>39000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>41500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>28600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>28700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>40900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>44900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>27000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>40100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>59800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>58900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>26400</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>48800</v>
       </c>
       <c r="AG24" s="3">
         <v>48800</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>48800</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2317,198 +2366,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E26" s="3">
         <v>81300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>136500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>102100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>85600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>539900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>141400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>144300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>126200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>559700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>202100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>217200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>177800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>166500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>168200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>118200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>109100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>104000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>105700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>137100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>84500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>88500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>96800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>129700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>80500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>102300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>129600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>140300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>77400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>104400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E27" s="3">
         <v>81300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>136500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>102100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>85600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>539900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>141400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>144300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>126200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>559700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>202100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>217200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>177800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>163600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>164600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>115800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>109100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>104100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>105600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>137500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>84700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>88400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>96700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>129600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>80600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>102300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>129500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>140300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>77400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>104300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2602,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2617,31 +2678,31 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>-1000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>146800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>62800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>47700</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>54700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>212700</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2649,14 +2710,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2668,37 +2729,40 @@
         <v>0</v>
       </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>3100</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>25700</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-700</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2792,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2887,198 +2954,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-12000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-1300</v>
       </c>
       <c r="N32" s="3">
         <v>-1300</v>
       </c>
       <c r="O32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P32" s="3">
         <v>3300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>31200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E33" s="3">
         <v>81300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>136500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>102100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>84600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>686700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>204200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>192000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>180900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>772400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>202100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>217200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>177800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>163600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>164600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>115800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>109100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>104100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>105600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>137500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>84700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>85200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>99800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>129600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>75000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>128000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>129500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>137700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>77400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>103600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3172,203 +3248,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E35" s="3">
         <v>81300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>136500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>102100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>84600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>686700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>204200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>192000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>180900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>772400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>202100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>217200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>177800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>163600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>164600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>115800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>109100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>104100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>105600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>137500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>84700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>85200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>99800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>129600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>75000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>128000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>129500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>137700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>77400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>103600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3402,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3437,103 +3523,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>359700</v>
+      </c>
+      <c r="E41" s="3">
         <v>366400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>453400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>681700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>539100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>642500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>345300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>360600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>378200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>471500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>460700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>460000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>356100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>419100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>464500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>398400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>359700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>387900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>336200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>276300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>281200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>262900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>389900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>345500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>244400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>323000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>277100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>252700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>210800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>251500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>278600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3627,388 +3717,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>615900</v>
+      </c>
+      <c r="E43" s="3">
         <v>534200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>578600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>621200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>559000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>521800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>936100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>998500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1011600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>885700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>921800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>844600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>828500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>734900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>765200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>657700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>678200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>624800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>640100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>706200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>650100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>571700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>635400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>657500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>631500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>555300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>594700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>595700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>564900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>550700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>568800</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1025200</v>
+      </c>
+      <c r="E44" s="3">
         <v>982300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>930000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>954500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>931100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1021300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1502300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1446700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1334700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1193800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1128300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1046800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>958400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>867200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>738300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>732300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>703100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>718600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>758800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>741900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>737900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>678900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>684300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>627000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>619200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>580800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>600100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>581400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>558800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>531100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>562500</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E45" s="3">
         <v>162800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>187700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>186200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>272000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>274800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>223900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>258000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>232200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>193500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>215200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>197500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>202900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>187300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>170000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>168900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>173000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>166900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>171600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>192500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>178800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>172600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>180600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>175500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>149400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>142600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>126400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>123300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>121600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>111900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>129800</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2172100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2045700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2149700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2443600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2301200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2460400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3007600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3063800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2956700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2744500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2726000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2548900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2345900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2208500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2138000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1957300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1914000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1898200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1906700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1916900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1848000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1686100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1890200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1805500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1644500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1601700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1598300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1553100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1456100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1445200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1539700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4102,198 +4207,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1153200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1148800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1052400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>980700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>917700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>902600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1274700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1266800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1248300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1201200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1134100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1107400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1084300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1087600</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>958600</v>
       </c>
       <c r="R48" s="3">
         <v>958600</v>
       </c>
       <c r="S48" s="3">
+        <v>958600</v>
+      </c>
+      <c r="T48" s="3">
         <v>966900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>989800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>966200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>978100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>981100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>813400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>776300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>737600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>742800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>740000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>690600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>675600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>665700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>662500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>642900</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3343400</v>
+      </c>
+      <c r="E49" s="3">
         <v>3261500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3304200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3332200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2634300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2641500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3922100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3814200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3870000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3848900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3867900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3891200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3900500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3815100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3196400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3199300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3219200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3259100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3271000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3314900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3323700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3327100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3397100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3055700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3069900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3074400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2958200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2925300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2930100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2940800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2948900</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4387,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4482,103 +4599,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>122800</v>
+      </c>
+      <c r="E52" s="3">
         <v>109000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>111800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>116700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>119500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>116400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>211200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>189300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>168000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>141600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>140800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>148500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>151400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>247500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>226000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>217100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>200000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>144200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>141700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>133500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>136400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>138000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>106100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>98300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>94800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>95300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>102200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>99400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>82200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>80000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4672,103 +4795,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6791500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6565000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6618100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6873200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5972700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6120900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8415600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8334100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8243000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7936200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7868800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7696000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7482100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7358700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6519000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6332300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6300100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6291300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6285600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6343400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6289200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5964600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6169700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5697100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5552000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5511400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5349300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5253400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5134100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5128500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5212600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4802,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4837,135 +4967,139 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>571400</v>
+      </c>
+      <c r="E57" s="3">
         <v>568100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>570400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>489500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>423700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>421600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>672600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>756300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>728100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>764900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>735700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>697500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>599200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>620500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>544100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>463900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>426400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>460000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>436500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>476600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>442000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>459000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>437700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>428700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>417100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>428800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>392500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>397000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>378900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>393800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>361900</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>599800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>599500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>599200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600300</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>400000</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -4973,8 +5107,8 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4983,34 +5117,34 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>399900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>399700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>399500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>749300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>350000</v>
-      </c>
-      <c r="X58" s="3">
-        <v>525000</v>
       </c>
       <c r="Y58" s="3">
         <v>525000</v>
       </c>
       <c r="Z58" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="AA58" s="3">
         <v>350000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
+      <c r="AB58" s="3">
+        <v>350000</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
@@ -5021,394 +5155,409 @@
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>491100</v>
+      </c>
+      <c r="E59" s="3">
         <v>632300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>621700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>551400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>390000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>523900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>775000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>685200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>626700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>806200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>793100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>667200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>597800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>724600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>590900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>488900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>419800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>549600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>540600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>469300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>446800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>508100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>488900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>451800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>373700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>478000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>460000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>394100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>328900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>449000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1062500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1200400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1192100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1640700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1413200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1544700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2047900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1441500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1354800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1971100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1528800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1364700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1197000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1345100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1135000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>952800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1246100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1409300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1376600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1695200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1238800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1492100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1451600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1230500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1140800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>906800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>852500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>791100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>707800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>842800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>776700</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3044700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2670100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2829300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2668500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2074900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2074300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2786900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3357900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3367900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2309800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2629100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2608300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2682800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2572200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2086500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2245900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2035200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1784600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1949000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1666000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2169700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1809000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1988400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1793300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1538000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1507600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1462200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1391900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1491500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1431100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1585800</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>403500</v>
+      </c>
+      <c r="E62" s="3">
         <v>401100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>377700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>386900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>402100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>415000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>550700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>582300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>605500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>590500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>656300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>679500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>677900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>665900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>668900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>670500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>660900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>669600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>623300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>637500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>633600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>483500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>496100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>498600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>514900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>495900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>488700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>501700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>504100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>491600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>489900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5502,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5597,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5692,103 +5847,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4510700</v>
+      </c>
+      <c r="E66" s="3">
         <v>4271600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4399100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4696100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3890200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4034000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5385500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5381700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5328200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4871400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4814200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4652500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4557700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4583200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3890400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3870500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3943100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3864700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3950200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3999900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4043700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3786400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3937800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3524000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3195200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2911900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2805000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2686200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2704900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2767000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2853800</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5822,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5917,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6012,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6107,8 +6275,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,103 +6373,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2701800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2605300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2554200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2475400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2402400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2323800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3277000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3145000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2989400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2807900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2670000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2539300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2358000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2180200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2052700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1954700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1872100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1763000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1692500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1648100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1541400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1448100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1393400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1350500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1249900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1076500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1002000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>892000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>814600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6392,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6487,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6582,103 +6765,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2280800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2293400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2219000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2177100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2082500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2086900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3030100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2952400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2914800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3064800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3054600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3043500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2924400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2775500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2628600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2461800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2357000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2426600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2335400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2343500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2245500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2178200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2231900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2173100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2356800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2599500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2544300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2567200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2429200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2361500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2358800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6772,203 +6961,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E81" s="3">
         <v>81300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>136500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>102100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>84600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>686700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>204200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>192000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>180900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>772400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>202100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>217200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>177800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>163600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>164600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>115800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>109100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>104100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>105600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>137500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>84700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>85200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>99800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>129600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>75000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>128000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>129500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>137700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>77400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>103600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7002,103 +7200,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46100</v>
+      </c>
+      <c r="E83" s="3">
         <v>57300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>34200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>31900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>191600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>48600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>46900</v>
       </c>
       <c r="K83" s="3">
         <v>46900</v>
       </c>
       <c r="L83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="M83" s="3">
         <v>189100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>46200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>47500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>47700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>46600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>39300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>40100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>37500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>40000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>36700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>38200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>37800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>40700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>37500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>37900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>33500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>34000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>32300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>32200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>31800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>33000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7192,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7287,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7382,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7477,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7572,103 +7786,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-71300</v>
+      </c>
+      <c r="E89" s="3">
         <v>220200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>332000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>427500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>76100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>566300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>246900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>225000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-183100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>688700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>168100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>331900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-69200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>318900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>246300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>274300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-13800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>283400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>241800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>201700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-89700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>260300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>206400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>189200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-51900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>247700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>181400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>189100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>269900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7702,103 +7922,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-80800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-69600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-42600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-71000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-60800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-101200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-47200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-40400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-84300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-23900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-49400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-27500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-43600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-39300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7892,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7987,103 +8214,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-169800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-80800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-65700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-848700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-42600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-455500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-211800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-54800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-114400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-207100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-47200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-799400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-23200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-77000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-49500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-27300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-25500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-25300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-65900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-496100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-42700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-174500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-50800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-178700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8117,103 +8350,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E96" s="3">
         <v>-29000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-29200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-29100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-29500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-145600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-36200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-36400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-37200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-143000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-35900</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-36000</v>
       </c>
       <c r="O96" s="3">
         <v>-36000</v>
       </c>
       <c r="P96" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-33400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-33300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-33100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-33500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-30700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-30600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-30700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-31000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-28100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-29000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-27400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-27700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-24500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8307,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8402,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8497,289 +8740,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>238700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-210700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-488400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>567100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-139300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>72500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-36000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-176100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>203200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-428600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-115700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-192200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>22800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>420400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-166600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-219500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>77300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-187800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-148900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-182400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>129400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-314200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>342600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>16200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-108300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>6000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>8200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-11100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-14700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>14400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>9900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>7000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-15000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-63100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-227700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>141600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-103600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>172200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-93600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>51100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>103500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-63200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-45700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>65700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>38600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-28500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>51600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>59500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-127200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>52400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>101100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>45900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>24400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>41900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-40700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-27100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>FBHS</t>
   </si>
@@ -656,440 +656,453 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1240000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1109600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1161300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1261200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1163700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1040000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4723000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1195500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1255400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1140200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4801100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1986300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1936100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1771000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1659700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1652100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1375800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1402700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1470500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1459000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1507200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1327900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1420700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1380800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1429000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1254600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1382500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1348600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1365400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1186800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1301600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1279000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>699000</v>
+      </c>
+      <c r="E9" s="3">
         <v>622000</v>
       </c>
-      <c r="E9" s="3">
-        <v>666400</v>
-      </c>
       <c r="F9" s="3">
+        <v>644700</v>
+      </c>
+      <c r="G9" s="3">
         <v>721100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>695600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>631700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2790100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>716600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>742000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>671800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2840600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1280000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1230300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1126900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1052000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1071500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>892900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>909500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>934600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>934800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>969600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>869100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>920300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>880800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>898900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>814600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>885700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>843200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>850500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>768500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>826400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>798200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>541000</v>
+      </c>
+      <c r="E10" s="3">
         <v>487600</v>
       </c>
-      <c r="E10" s="3">
-        <v>494900</v>
-      </c>
       <c r="F10" s="3">
+        <v>516600</v>
+      </c>
+      <c r="G10" s="3">
         <v>540100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>468100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>408300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1932900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>478900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>513400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>468400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1960500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>706300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>705800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>644100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>607700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>580600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>482900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>493200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>535900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>524200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>537600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>458800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>500400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>500000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>530100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>440000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>496800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>505400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>514900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>418300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>475200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>480800</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1124,8 +1137,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,8 +1236,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,204 +1337,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E14" s="3">
         <v>2800</v>
       </c>
-      <c r="E14" s="3">
-        <v>37100</v>
-      </c>
       <c r="F14" s="3">
+        <v>58800</v>
+      </c>
+      <c r="G14" s="3">
         <v>3700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>22200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>32400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>20600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>27000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>23400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>23000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>35000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>43400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>38400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>16300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>18100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E15" s="3">
         <v>17800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18800</v>
-      </c>
-      <c r="G15" s="3">
-        <v>12600</v>
       </c>
       <c r="H15" s="3">
         <v>12600</v>
       </c>
       <c r="I15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="J15" s="3">
         <v>48300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12500</v>
-      </c>
-      <c r="K15" s="3">
-        <v>11600</v>
       </c>
       <c r="L15" s="3">
         <v>11600</v>
       </c>
       <c r="M15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="N15" s="3">
         <v>46400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>15900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>16000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>10900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>10500</v>
-      </c>
-      <c r="S15" s="3">
-        <v>10300</v>
       </c>
       <c r="T15" s="3">
         <v>10300</v>
       </c>
       <c r="U15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="V15" s="3">
         <v>11400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>9900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>10100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>10800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>8900</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>8200</v>
       </c>
       <c r="AB15" s="3">
         <v>8200</v>
       </c>
       <c r="AC15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AD15" s="3">
         <v>8100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>7500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>8000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>8100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>7700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1549,204 +1575,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1040900</v>
+      </c>
+      <c r="E17" s="3">
         <v>954200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1027400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1064700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1011100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>908200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3948700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1002800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1035900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>960400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3990000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1699700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1641200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1522600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1426500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1411900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1202800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1247700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1278000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1291000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1304800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1192300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1280600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1233700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1240400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1219700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1156200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1071900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1095900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>199100</v>
+      </c>
+      <c r="E18" s="3">
         <v>155400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>133900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>196500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>152600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>131800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>774300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>192700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>219500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>179800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>811100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>286600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>294900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>248400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>233200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>240200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>173000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>155000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>192500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>168000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>202400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>135600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>140100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>147100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>188600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>119400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>162800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>199500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>209200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>114900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>166400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>183100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1781,498 +1814,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>1300</v>
       </c>
       <c r="O20" s="3">
         <v>1300</v>
       </c>
       <c r="P20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-31200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>258200</v>
+      </c>
+      <c r="E21" s="3">
         <v>201400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>189800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>251300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>192000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>170000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>977900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>244100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>266600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>228800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>999800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>334100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>343700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>292800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>279700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>281600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>218300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>198600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>201300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>205000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>241300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>174600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>181300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>194200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>229900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>155700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>189300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>234000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>243700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>147500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>197800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>212400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E22" s="3">
         <v>30100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>33300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>26800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>119200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>33000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>30500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>21700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>84300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>22200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>22100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>22400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>24500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>17400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>14700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12900</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>12300</v>
       </c>
       <c r="AE22" s="3">
         <v>12300</v>
       </c>
       <c r="AF22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AG22" s="3">
         <v>11900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>11600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>170500</v>
+      </c>
+      <c r="E23" s="3">
         <v>125200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>103900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>172600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>130100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>111300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>667100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>162500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>189200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>160200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>726400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>267300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>275000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>223700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>213600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>222200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>156000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>139000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>138900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>144700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>178600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>113100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>117200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>137700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>174600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>107500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>142400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>189400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>199200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>103800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>153200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E24" s="3">
         <v>28800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>22600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>36100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>25700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>127200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>44900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>34000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>166700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>65200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>57800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>45900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>47100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>54000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>37800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>29900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>34900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>39000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>41500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>28600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>28700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>40900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>44900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>27000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>40100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>59800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>58900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>26400</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>48800</v>
       </c>
       <c r="AH24" s="3">
         <v>48800</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>48800</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2369,204 +2418,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E26" s="3">
         <v>96400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>81300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>136500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>102100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>85600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>539900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>141400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>144300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>126200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>559700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>202100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>217200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>177800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>166500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>168200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>118200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>109100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>104000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>105700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>137100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>84500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>88500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>96800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>129700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>80500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>102300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>129600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>140300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>77400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>104400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E27" s="3">
         <v>96400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>81300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>136500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>102100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>85600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>539900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>141400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>144300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>126200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>559700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>202100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>217200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>177800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>163600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>164600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>115800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>109100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>104100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>105600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>137500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>84700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>88400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>96700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>129600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>80600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>102300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>129500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>140300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>77400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>104300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2721,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2681,31 +2742,31 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-1000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>146800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>62800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>47700</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>54700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>212700</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2713,14 +2774,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2732,37 +2793,40 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>3100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>25700</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>-700</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2859,8 +2923,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2957,204 +3024,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-1300</v>
       </c>
       <c r="O32" s="3">
         <v>-1300</v>
       </c>
       <c r="P32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="Q32" s="3">
         <v>3300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>31200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E33" s="3">
         <v>96400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>81300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>136500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>102100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>84600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>686700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>204200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>192000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>180900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>772400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>202100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>217200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>177800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>163600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>164600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>115800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>109100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>104100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>105600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>137500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>84700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>85200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>99800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>129600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>75000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>128000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>129500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>137700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>77400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>103600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3251,209 +3327,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E35" s="3">
         <v>96400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>81300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>136500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>102100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>84600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>686700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>204200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>192000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>180900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>772400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>202100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>217200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>177800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>163600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>164600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>115800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>109100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>104100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>105600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>137500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>84700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>85200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>99800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>129600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>75000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>128000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>129500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>137700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>77400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>103600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,8 +3573,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3524,106 +3610,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>352600</v>
+      </c>
+      <c r="E41" s="3">
         <v>359700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>366400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>453400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>681700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>539100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>642500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>345300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>360600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>378200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>471500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>460700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>460000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>356100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>419100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>464500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>398400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>359700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>387900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>336200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>276300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>281200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>262900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>389900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>345500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>244400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>323000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>277100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>252700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>210800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>251500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>278600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3720,400 +3810,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>593600</v>
+      </c>
+      <c r="E43" s="3">
         <v>615900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>534200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>578600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>621200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>559000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>521800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>936100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>998500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1011600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>885700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>921800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>844600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>828500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>734900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>765200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>657700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>678200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>624800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>640100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>706200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>650100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>571700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>635400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>657500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>631500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>555300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>594700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>595700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>564900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>550700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>568800</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>990500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1025200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>982300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>930000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>954500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>931100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1021300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1502300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1446700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1334700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1193800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1128300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1046800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>958400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>867200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>738300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>732300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>703100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>718600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>758800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>741900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>737900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>678900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>684300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>627000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>619200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>580800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>600100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>581400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>558800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>531100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>562500</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>145200</v>
+      </c>
+      <c r="E45" s="3">
         <v>171300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>162800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>187700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>186200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>272000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>274800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>223900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>258000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>232200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>193500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>215200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>197500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>202900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>187300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>170000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>168900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>173000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>166900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>171600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>192500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>178800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>172600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>180600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>175500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>149400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>142600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>126400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>123300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>121600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>111900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>129800</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2081900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2172100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2045700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2149700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2443600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2301200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2460400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3007600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3063800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2956700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2744500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2726000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2548900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2345900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2208500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2138000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1957300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1914000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1898200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1906700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1916900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1848000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1686100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1890200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1805500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1644500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1601700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1598300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1553100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1456100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1445200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1539700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4210,204 +4315,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1140000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1153200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1148800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1052400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>980700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>917700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>902600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1274700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1266800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1248300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1201200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1134100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1107400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1084300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1087600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>958600</v>
       </c>
       <c r="S48" s="3">
         <v>958600</v>
       </c>
       <c r="T48" s="3">
+        <v>958600</v>
+      </c>
+      <c r="U48" s="3">
         <v>966900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>989800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>966200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>978100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>981100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>813400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>776300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>737600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>742800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>740000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>690600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>675600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>665700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>662500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>642900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3331000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3343400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3261500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3304200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3332200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2634300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2641500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3922100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3814200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3870000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3848900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3867900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3891200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3900500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3815100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3196400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3199300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3219200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3259100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3271000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3314900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3323700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3327100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3397100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3055700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3069900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3074400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2958200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2925300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2930100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2940800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2948900</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4504,8 +4618,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4602,106 +4719,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E52" s="3">
         <v>122800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>109000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>111800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>116700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>119500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>116400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>211200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>189300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>168000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>141600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>140800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>148500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>151400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>247500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>226000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>217100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>200000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>144200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>141700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>133500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>136400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>138000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>106100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>98300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>94800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>95300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>102200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>99400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>82200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>80000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4798,106 +4921,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6673900</v>
+      </c>
+      <c r="E54" s="3">
         <v>6791500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6565000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6618100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6873200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5972700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6120900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8415600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8334100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8243000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7936200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7868800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7696000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7482100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7358700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6519000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6332300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6300100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6291300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6285600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6343400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6289200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5964600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6169700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5697100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5552000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5511400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5349300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5253400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5134100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5128500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5212600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,8 +5061,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4968,141 +5098,145 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>554400</v>
+      </c>
+      <c r="E57" s="3">
         <v>571400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>568100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>570400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>489500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>423700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>421600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>672600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>756300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>728100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>764900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>735700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>697500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>599200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>620500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>544100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>463900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>426400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>460000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>436500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>476600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>442000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>459000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>437700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>428700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>417100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>428800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>392500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>397000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>378900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>393800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>361900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="D58" s="3">
+        <v>499300</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>599800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>599500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>599200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>400000</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -5110,8 +5244,8 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5120,34 +5254,34 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>399900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>399700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>399500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>749300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>350000</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>525000</v>
       </c>
       <c r="Z58" s="3">
         <v>525000</v>
       </c>
       <c r="AA58" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="AB58" s="3">
         <v>350000</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
+      <c r="AC58" s="3">
+        <v>350000</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
@@ -5158,406 +5292,421 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>494300</v>
+      </c>
+      <c r="E59" s="3">
         <v>491100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>632300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>621700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>551400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>390000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>523900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>775000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>685200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>626700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>806200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>793100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>667200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>597800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>724600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>590900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>488900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>419800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>549600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>540600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>469300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>446800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>508100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>488900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>451800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>373700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>478000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>460000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>394100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>328900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>449000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1548000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1062500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1200400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1192100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1640700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1413200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1544700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2047900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1441500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1354800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1971100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1528800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1364700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1197000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1345100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1135000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>952800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1246100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1409300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1376600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1695200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1238800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1492100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1451600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1230500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1140800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>906800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>852500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>791100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>707800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>842800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>776700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2401700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3044700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2670100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2829300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2668500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2074900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2074300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2786900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3357900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3367900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2309800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2629100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2608300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2682800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2572200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2086500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2245900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2035200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1784600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1949000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1666000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2169700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1809000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1988400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1793300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1538000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1507600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1462200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1391900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1491500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1431100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1585800</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>393600</v>
+      </c>
+      <c r="E62" s="3">
         <v>403500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>401100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>377700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>386900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>402100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>415000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>550700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>582300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>605500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>590500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>656300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>679500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>677900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>665900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>668900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>670500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>660900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>669600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>623300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>637500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>633600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>483500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>496100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>498600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>514900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>495900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>488700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>501700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>504100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>491600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>489900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5654,8 +5803,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5752,8 +5904,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5850,106 +6005,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4343300</v>
+      </c>
+      <c r="E66" s="3">
         <v>4510700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4271600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4399100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4696100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3890200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4034000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5385500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5381700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5328200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4871400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4814200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4652500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4557700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4583200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3890400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3870500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3943100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3864700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3950200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3999900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4043700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3786400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3937800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3524000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3195200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2911900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2805000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2686200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2704900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2767000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2853800</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5984,8 +6145,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6082,8 +6244,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6180,8 +6345,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6278,8 +6446,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6376,106 +6547,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2805500</v>
+      </c>
+      <c r="E72" s="3">
         <v>2701800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2605300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2554200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2475400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2402400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2323800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3277000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3145000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2989400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2807900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2670000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2539300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2358000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2180200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2052700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1954700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1872100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1763000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1692500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1648100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1541400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1448100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1393400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1350500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1249900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1076500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1002000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>892000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>814600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6572,8 +6749,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6670,8 +6850,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6768,106 +6951,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2330600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2280800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2293400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2219000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2177100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2082500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2086900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3030100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2952400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2914800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3064800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3054600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3043500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2924400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2775500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2628600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2461800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2357000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2426600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2335400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2343500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2245500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2178200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2231900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2173100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2356800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2599500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2544300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2567200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2429200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2361500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2358800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6964,209 +7153,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>133900</v>
+      </c>
+      <c r="E81" s="3">
         <v>96400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>81300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>136500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>102100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>84600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>686700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>204200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>192000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>180900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>772400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>202100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>217200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>177800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>163600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>164600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>115800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>109100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>104100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>105600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>137500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>84700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>85200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>99800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>129600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>75000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>128000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>129500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>137700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>77400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>103600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7201,106 +7399,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E83" s="3">
         <v>46100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>57300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>34200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>191600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>48600</v>
-      </c>
-      <c r="K83" s="3">
-        <v>46900</v>
       </c>
       <c r="L83" s="3">
         <v>46900</v>
       </c>
       <c r="M83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="N83" s="3">
         <v>189100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>46200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>47500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>47700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>46600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>39300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>40100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>37500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>40000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>36700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>38200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>37800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>40700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>37500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>37900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>33500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>34000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>32300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>32200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>31800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>33000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7397,8 +7599,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7495,8 +7700,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7593,8 +7801,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +7902,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7789,106 +8003,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>261500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-71300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>220200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>332000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>427500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>76100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>566300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>246900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>225000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-183100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>688700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>168100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>331900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>318900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>246300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>274300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-13800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>283400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>241800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>201700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-89700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>260300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>206400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>189200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-51900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>247700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>181400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>189100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>269900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7923,106 +8143,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-64600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-80800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-69600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-42600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-71000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-59500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-60800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-101200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-47200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-40400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-84300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-23900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-26900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-49400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-43600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-39300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8119,8 +8343,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8217,106 +8444,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-60400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-169800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-80800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-65700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-848700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-42600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-455500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-211800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-114400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-207100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-47200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-40400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-799400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-23900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-23200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-77000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-49500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-27300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-25500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-25300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-65900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-496100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-42700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-174500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-50800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-178700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8351,8 +8584,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8360,97 +8594,100 @@
         <v>-30100</v>
       </c>
       <c r="E96" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="F96" s="3">
         <v>-29000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-29200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-29100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-29500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-145600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-36200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-36400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-37200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-143000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-35900</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-36000</v>
       </c>
       <c r="P96" s="3">
         <v>-36000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-33400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-33300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-33100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-33500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-30700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-30600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-30700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-31000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-28100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-28500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-29000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-27400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-27700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-24500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8547,8 +8784,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8645,8 +8885,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8743,298 +8986,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="E100" s="3">
         <v>238700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-210700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-488400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>567100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-139300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>72500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-176100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>203200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-428600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-115700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-192200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>22800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>420400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-166600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-219500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>77300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-187800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-148900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-182400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>129400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-314200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>342600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>16200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-108300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>6000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-11100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-14700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>14400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>9900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>7000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-15000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-63100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-227700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>141600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-103600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>172200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-93600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>51100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>103500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-63200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-45700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>65700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>38600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-28500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>51600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>59500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-127200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>52400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>101100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>45900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>24400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>41900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-40700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-27100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>FBHS</t>
   </si>
@@ -656,453 +656,466 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1155300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1240000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1109600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1161300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1261200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1163700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1040000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4723000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1195500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1255400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1140200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4801100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1986300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1936100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1771000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1659700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1652100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1375800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1402700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1470500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1459000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1507200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1327900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1420700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1380800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1429000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1254600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1382500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1348600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1365400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1186800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1301600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1279000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>625500</v>
+      </c>
+      <c r="E9" s="3">
         <v>699000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>622000</v>
       </c>
-      <c r="F9" s="3">
-        <v>644700</v>
-      </c>
       <c r="G9" s="3">
+        <v>655600</v>
+      </c>
+      <c r="H9" s="3">
         <v>721100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>695600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>631700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2790100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>716600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>742000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>671800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2840600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1280000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1230300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1126900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1052000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1071500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>892900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>909500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>934600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>934800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>969600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>869100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>920300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>880800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>898900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>814600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>885700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>843200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>850500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>768500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>826400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>798200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>529800</v>
+      </c>
+      <c r="E10" s="3">
         <v>541000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>487600</v>
       </c>
-      <c r="F10" s="3">
-        <v>516600</v>
-      </c>
       <c r="G10" s="3">
+        <v>505700</v>
+      </c>
+      <c r="H10" s="3">
         <v>540100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>468100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>408300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1932900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>478900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>513400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>468400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1960500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>706300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>705800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>644100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>607700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>580600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>482900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>493200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>535900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>524200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>537600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>458800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>500400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>500000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>530100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>440000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>496800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>505400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>514900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>418300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>475200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>480800</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1138,8 +1151,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,8 +1166,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>64600</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1239,8 +1253,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1340,210 +1357,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E14" s="3">
         <v>3900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2800</v>
       </c>
-      <c r="F14" s="3">
-        <v>58800</v>
-      </c>
       <c r="G14" s="3">
+        <v>47900</v>
+      </c>
+      <c r="H14" s="3">
         <v>3700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>22200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>32400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>20600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>27000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>23400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>14000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>23000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>35000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>43400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>38400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>16300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>18100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>6100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E15" s="3">
         <v>18300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18800</v>
-      </c>
-      <c r="H15" s="3">
-        <v>12600</v>
       </c>
       <c r="I15" s="3">
         <v>12600</v>
       </c>
       <c r="J15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K15" s="3">
         <v>48300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12500</v>
-      </c>
-      <c r="L15" s="3">
-        <v>11600</v>
       </c>
       <c r="M15" s="3">
         <v>11600</v>
       </c>
       <c r="N15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="O15" s="3">
         <v>46400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>15900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>16000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>10900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>10500</v>
-      </c>
-      <c r="T15" s="3">
-        <v>10300</v>
       </c>
       <c r="U15" s="3">
         <v>10300</v>
       </c>
       <c r="V15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="W15" s="3">
         <v>11400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>9900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>10000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>10800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>8900</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>8200</v>
       </c>
       <c r="AC15" s="3">
         <v>8200</v>
       </c>
       <c r="AD15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AE15" s="3">
         <v>8100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>7500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>8000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>8100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>7700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,210 +1602,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1040900</v>
+        <v>942800</v>
       </c>
       <c r="E17" s="3">
-        <v>954200</v>
+        <v>1037000</v>
       </c>
       <c r="F17" s="3">
-        <v>1027400</v>
+        <v>951400</v>
       </c>
       <c r="G17" s="3">
-        <v>1064700</v>
+        <v>977900</v>
       </c>
       <c r="H17" s="3">
-        <v>1011100</v>
+        <v>1061000</v>
       </c>
       <c r="I17" s="3">
-        <v>908200</v>
+        <v>988900</v>
       </c>
       <c r="J17" s="3">
+        <v>905100</v>
+      </c>
+      <c r="K17" s="3">
         <v>3948700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1002800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1035900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>960400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3990000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1699700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1641200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1522600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1426500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1411900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1202800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1247700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1278000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1291000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1304800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1192300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1280600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1233700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1240400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1219700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1156200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1071900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1095900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>199100</v>
+        <v>212500</v>
       </c>
       <c r="E18" s="3">
-        <v>155400</v>
+        <v>203000</v>
       </c>
       <c r="F18" s="3">
-        <v>133900</v>
+        <v>158200</v>
       </c>
       <c r="G18" s="3">
-        <v>196500</v>
+        <v>183400</v>
       </c>
       <c r="H18" s="3">
-        <v>152600</v>
+        <v>200200</v>
       </c>
       <c r="I18" s="3">
-        <v>131800</v>
+        <v>174800</v>
       </c>
       <c r="J18" s="3">
+        <v>134900</v>
+      </c>
+      <c r="K18" s="3">
         <v>774300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>192700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>219500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>179800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>811100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>286600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>294900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>248400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>233200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>240200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>173000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>155000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>192500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>168000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>202400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>135600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>140100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>147100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>188600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>119400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>162800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>199500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>209200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>114900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>166400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>183100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1815,513 +1848,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3700</v>
+        <v>-1600</v>
       </c>
       <c r="E20" s="3">
-        <v>-100</v>
+        <v>-3700</v>
       </c>
       <c r="F20" s="3">
-        <v>-1400</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
-        <v>9400</v>
+        <v>17200</v>
       </c>
       <c r="H20" s="3">
-        <v>5200</v>
+        <v>-9400</v>
       </c>
       <c r="I20" s="3">
-        <v>6300</v>
+        <v>-5200</v>
       </c>
       <c r="J20" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="K20" s="3">
         <v>12000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>1300</v>
       </c>
       <c r="P20" s="3">
         <v>1300</v>
       </c>
       <c r="Q20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R20" s="3">
         <v>-3300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-31200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>258200</v>
+        <v>233200</v>
       </c>
       <c r="E21" s="3">
-        <v>201400</v>
+        <v>225000</v>
       </c>
       <c r="F21" s="3">
-        <v>189800</v>
+        <v>175900</v>
       </c>
       <c r="G21" s="3">
-        <v>251300</v>
+        <v>184300</v>
       </c>
       <c r="H21" s="3">
-        <v>192000</v>
+        <v>228400</v>
       </c>
       <c r="I21" s="3">
-        <v>170000</v>
+        <v>192600</v>
       </c>
       <c r="J21" s="3">
+        <v>153800</v>
+      </c>
+      <c r="K21" s="3">
         <v>977900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>244100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>266600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>228800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>999800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>334100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>343700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>292800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>279700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>281600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>218300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>198600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>201300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>205000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>241300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>174600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>181300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>194200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>229900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>155700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>189300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>234000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>243700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>147500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>197800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>212400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E22" s="3">
         <v>32300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>33300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>26800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>119200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>33000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>30500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>84300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>20100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>22200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>22100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>24500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>17400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>14700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12900</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>12300</v>
       </c>
       <c r="AF22" s="3">
         <v>12300</v>
       </c>
       <c r="AG22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AH22" s="3">
         <v>11900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>11600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>176500</v>
+      </c>
+      <c r="E23" s="3">
         <v>170500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>125200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>103900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>172600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>130100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>111300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>667100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>162500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>189200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>160200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>726400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>267300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>275000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>223700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>213600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>222200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>156000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>139000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>138900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>144700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>178600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>113100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>117200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>137700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>174600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>107500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>142400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>189400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>199200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>103800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>153200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E24" s="3">
         <v>36600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>22600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>36100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>127200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>44900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>34000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>166700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>65200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>57800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>45900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>47100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>54000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>37800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>29900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>34900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>39000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>41500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>28600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>28700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>40900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>44900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>27000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>40100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>59800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>58900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>26400</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>48800</v>
       </c>
       <c r="AI24" s="3">
         <v>48800</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>48800</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,210 +2470,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E26" s="3">
         <v>133900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>96400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>81300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>136500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>102100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>85600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>539900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>141400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>144300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>126200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>559700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>202100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>217200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>177800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>166500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>168200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>118200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>109100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>104000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>105700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>137100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>84500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>88500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>96800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>129700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>80500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>102300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>129600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>140300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>77400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>104400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E27" s="3">
         <v>133900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>96400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>81300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>136500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>102100</v>
       </c>
-      <c r="I27" s="3">
-        <v>85600</v>
-      </c>
       <c r="J27" s="3">
+        <v>84600</v>
+      </c>
+      <c r="K27" s="3">
         <v>539900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>141400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>144300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>126200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>559700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>202100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>217200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>177800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>163600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>164600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>115800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>109100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>104100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>105600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>137500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>84700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>88400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>96700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>129600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>80600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>102300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>129500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>140300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>77400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>104300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2782,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2745,31 +2806,31 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-1000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>146800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>62800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>47700</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>54700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>212700</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2777,14 +2838,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2796,37 +2857,40 @@
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>3100</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>25700</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-700</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2990,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,210 +3094,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3700</v>
+        <v>1600</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>3700</v>
       </c>
       <c r="F32" s="3">
-        <v>1400</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
-        <v>-9400</v>
+        <v>-17200</v>
       </c>
       <c r="H32" s="3">
-        <v>-5200</v>
+        <v>9400</v>
       </c>
       <c r="I32" s="3">
-        <v>-6300</v>
+        <v>5200</v>
       </c>
       <c r="J32" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-12000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-1300</v>
       </c>
       <c r="P32" s="3">
         <v>-1300</v>
       </c>
       <c r="Q32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="R32" s="3">
         <v>3300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>31200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E33" s="3">
         <v>133900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>96400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>81300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>136500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>102100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>84600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>686700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>204200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>192000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>180900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>772400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>202100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>217200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>177800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>163600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>164600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>115800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>109100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>104100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>105600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>137500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>84700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>85200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>99800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>129600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>75000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>128000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>129500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>137700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>77400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>103600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,215 +3406,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E35" s="3">
         <v>133900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>96400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>81300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>136500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>102100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>84600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>686700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>204200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>192000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>180900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>772400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>202100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>217200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>177800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>163600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>164600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>115800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>109100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>104100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>105600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>137500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>84700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>85200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>99800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>129600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>75000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>128000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>129500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>137700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>77400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>103600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3659,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,109 +3697,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>344800</v>
+      </c>
+      <c r="E41" s="3">
         <v>352600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>359700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>366400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>453400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>681700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>539100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>642500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>345300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>360600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>378200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>471500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>460700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>460000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>356100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>419100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>464500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>398400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>359700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>387900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>336200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>276300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>281200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>262900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>389900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>345500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>244400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>323000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>277100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>252700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>210800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>251500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>278600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3736,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3813,435 +3903,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>555900</v>
+      </c>
+      <c r="E43" s="3">
         <v>593600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>615900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>534200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>578600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>621200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>559000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>521800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>936100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>998500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1011600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>885700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>921800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>844600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>828500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>734900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>765200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>657700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>678200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>624800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>640100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>706200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>650100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>571700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>635400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>657500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>631500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>555300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>594700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>595700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>564900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>550700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>568800</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>962600</v>
+      </c>
+      <c r="E44" s="3">
         <v>990500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1025200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>982300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>930000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>954500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>931100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1021300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1502300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1446700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1334700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1193800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1128300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1046800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>958400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>867200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>738300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>732300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>703100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>718600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>758800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>741900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>737900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>678900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>684300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>627000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>619200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>580800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>600100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>581400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>558800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>531100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>562500</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>145200</v>
+        <v>153400</v>
       </c>
       <c r="E45" s="3">
-        <v>171300</v>
+        <v>142700</v>
       </c>
       <c r="F45" s="3">
-        <v>162800</v>
+        <v>145400</v>
       </c>
       <c r="G45" s="3">
-        <v>187700</v>
+        <v>135900</v>
       </c>
       <c r="H45" s="3">
-        <v>186200</v>
+        <v>184700</v>
       </c>
       <c r="I45" s="3">
-        <v>272000</v>
+        <v>183900</v>
       </c>
       <c r="J45" s="3">
+        <v>196300</v>
+      </c>
+      <c r="K45" s="3">
         <v>274800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>223900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>258000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>232200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>193500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>215200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>197500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>202900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>187300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>170000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>168900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>173000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>166900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>171600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>192500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>178800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>172600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>180600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>175500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>149400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>142600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>126400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>123300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>121600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>111900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>129800</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2019100</v>
+      </c>
+      <c r="E46" s="3">
         <v>2081900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2172100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2045700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2149700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2443600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2301200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2460400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3007600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3063800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2956700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2744500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2726000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2548900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2345900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2208500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2138000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1957300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1914000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1898200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1906700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1916900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1848000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1686100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1890200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1805500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1644500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1601700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1598300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1553100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1456100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1445200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1539700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>3500</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4318,210 +4423,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1138300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1140000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1153200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1148800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1052400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>980700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>917700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>902600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1274700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1266800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1248300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1201200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1134100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1107400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1084300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1087600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>958600</v>
       </c>
       <c r="T48" s="3">
         <v>958600</v>
       </c>
       <c r="U48" s="3">
+        <v>958600</v>
+      </c>
+      <c r="V48" s="3">
         <v>966900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>989800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>966200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>978100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>981100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>813400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>776300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>737600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>742800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>740000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>690600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>675600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>665700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>662500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>642900</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3329000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3331000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3343400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3261500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3304200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3332200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2634300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2641500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3922100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3814200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3870000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3848900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3867900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3891200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3900500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3815100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3196400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3199300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3219200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3259100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3271000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3314900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3323700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3327100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3397100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3055700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3069900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3074400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2958200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2925300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2930100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2940800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2948900</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4735,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,109 +4839,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E52" s="3">
         <v>121000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>122800</v>
       </c>
-      <c r="F52" s="3">
-        <v>109000</v>
-      </c>
       <c r="G52" s="3">
+        <v>87000</v>
+      </c>
+      <c r="H52" s="3">
         <v>111800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>116700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>119500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>116400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>211200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>189300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>168000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>141600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>140800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>148500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>151400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>247500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>226000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>217100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>200000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>144200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>141700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>133500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>136400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>138000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>106100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>98300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>94800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>95300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>102200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>99400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>82200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>80000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,109 +5047,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6598400</v>
+      </c>
+      <c r="E54" s="3">
         <v>6673900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6791500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6565000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6618100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6873200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5972700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6120900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8415600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8334100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8243000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7936200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7868800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7696000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7482100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7358700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6519000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6332300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6300100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6291300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6285600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6343400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6289200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5964600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6169700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5697100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5552000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5511400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5349300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5253400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5134100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5128500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5212600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5191,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,147 +5229,151 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>493300</v>
+      </c>
+      <c r="E57" s="3">
         <v>554400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>571400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>568100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>570400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>489500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>423700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>421600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>672600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>756300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>728100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>764900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>735700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>697500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>599200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>620500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>544100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>463900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>426400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>460000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>436500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>476600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>442000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>459000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>437700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>428700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>417100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>428800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>392500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>397000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>378900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>393800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>361900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>499500</v>
+      </c>
+      <c r="E58" s="3">
         <v>499300</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>37100</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>599800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>599500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>599200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>600300</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>400000</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
@@ -5247,8 +5381,8 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -5257,34 +5391,34 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>399900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>399700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>399500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>749300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>350000</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>525000</v>
       </c>
       <c r="AA58" s="3">
         <v>525000</v>
       </c>
       <c r="AB58" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="AC58" s="3">
         <v>350000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>8</v>
+      <c r="AD58" s="3">
+        <v>350000</v>
       </c>
       <c r="AE58" s="3" t="s">
         <v>8</v>
@@ -5295,418 +5429,433 @@
       <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
+      <c r="AH58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>539400</v>
+      </c>
+      <c r="E59" s="3">
         <v>494300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>491100</v>
       </c>
-      <c r="F59" s="3">
-        <v>632300</v>
-      </c>
       <c r="G59" s="3">
+        <v>248600</v>
+      </c>
+      <c r="H59" s="3">
         <v>621700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>551400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>390000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>523900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>775000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>685200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>626700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>806200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>793100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>667200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>597800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>724600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>590900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>488900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>419800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>549600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>540600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>469300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>446800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>508100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>488900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>451800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>373700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>478000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>460000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>394100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>328900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>449000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1532200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1548000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1062500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1200400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1192100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1640700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1413200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1544700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2047900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1441500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1354800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1971100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1528800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1364700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1197000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1345100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1135000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>952800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1246100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1409300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1376600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1695200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1238800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1492100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1451600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1230500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1140800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>906800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>852500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>791100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>707800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>842800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>776700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2401700</v>
+        <v>2405600</v>
       </c>
       <c r="E61" s="3">
-        <v>3044700</v>
+        <v>2536000</v>
       </c>
       <c r="F61" s="3">
-        <v>2670100</v>
+        <v>3185200</v>
       </c>
       <c r="G61" s="3">
-        <v>2829300</v>
+        <v>2813400</v>
       </c>
       <c r="H61" s="3">
-        <v>2668500</v>
+        <v>2921400</v>
       </c>
       <c r="I61" s="3">
-        <v>2074900</v>
+        <v>2757500</v>
       </c>
       <c r="J61" s="3">
+        <v>2164900</v>
+      </c>
+      <c r="K61" s="3">
         <v>2074300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2786900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3357900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3367900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2309800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2629100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2608300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2682800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2572200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2086500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2245900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2035200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1784600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1949000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1666000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2169700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1809000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1988400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1793300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1538000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1507600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1462200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1391900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1491500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1431100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1585800</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>393600</v>
+        <v>85900</v>
       </c>
       <c r="E62" s="3">
-        <v>403500</v>
+        <v>86200</v>
       </c>
       <c r="F62" s="3">
-        <v>401100</v>
+        <v>89200</v>
       </c>
       <c r="G62" s="3">
-        <v>377700</v>
+        <v>99200</v>
       </c>
       <c r="H62" s="3">
-        <v>386900</v>
+        <v>100400</v>
       </c>
       <c r="I62" s="3">
-        <v>402100</v>
+        <v>93600</v>
       </c>
       <c r="J62" s="3">
+        <v>102400</v>
+      </c>
+      <c r="K62" s="3">
         <v>415000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>550700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>582300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>605500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>590500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>656300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>679500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>677900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>665900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>668900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>670500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>660900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>669600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>623300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>637500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>633600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>483500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>496100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>498600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>514900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>495900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>488700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>501700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>504100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>491600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>489900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5955,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6059,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,109 +6163,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4202500</v>
+      </c>
+      <c r="E66" s="3">
         <v>4343300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4510700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4271600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4399100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4696100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3890200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4034000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5385500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5381700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5328200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4871400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4814200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4652500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4557700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4583200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3890400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3870500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3943100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3864700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3950200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3999900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4043700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3786400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3937800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3524000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3195200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2911900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2805000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2686200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2704900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2767000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2853800</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6307,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6409,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6513,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6449,8 +6617,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,109 +6721,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2882500</v>
+      </c>
+      <c r="E72" s="3">
         <v>2805500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2701800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2605300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2554200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2475400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2402400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2323800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3277000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3145000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2989400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2807900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2670000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2539300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2358000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2180200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2052700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1954700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1872100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1763000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1692500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1648100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1541400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1448100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1393400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1350500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1249900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1076500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1002000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>892000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>814600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6929,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7033,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,109 +7137,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2395900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2330600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2280800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2293400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2219000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2177100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2082500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2086900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3030100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2952400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2914800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3064800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3054600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3043500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2924400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2775500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2628600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2461800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2357000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2426600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2335400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2343500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2245500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2178200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2231900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2173100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2356800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2599500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2544300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2567200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2429200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2361500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2358800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,215 +7345,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E81" s="3">
         <v>133900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>96400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>81300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>136500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>102100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>84600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>686700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>204200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>192000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>180900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>772400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>202100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>217200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>177800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>163600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>164600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>115800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>109100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>104100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>105600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>137500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>84700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>85200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>99800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>129600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>75000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>128000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>129500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>137700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>77400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>103600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,109 +7598,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>55400</v>
+        <v>26600</v>
       </c>
       <c r="E83" s="3">
-        <v>46100</v>
+        <v>21600</v>
       </c>
       <c r="F83" s="3">
-        <v>57300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>45400</v>
+        <v>19300</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H83" s="3">
-        <v>34200</v>
+        <v>31800</v>
       </c>
       <c r="I83" s="3">
-        <v>31900</v>
+        <v>30800</v>
       </c>
       <c r="J83" s="3">
+        <v>30900</v>
+      </c>
+      <c r="K83" s="3">
         <v>191600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>48600</v>
-      </c>
-      <c r="L83" s="3">
-        <v>46900</v>
       </c>
       <c r="M83" s="3">
         <v>46900</v>
       </c>
       <c r="N83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="O83" s="3">
         <v>189100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>46200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>47500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>47700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>46600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>39300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>40100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>37500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>40000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>36700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>38200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>37800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>40700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>37500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>37900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>33500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>34000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>32300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>32200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>31800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>33000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7804,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7908,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8012,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8116,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,109 +8220,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E89" s="3">
         <v>261500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-71300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>220200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>332000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>427500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>76100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>566300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>246900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>225000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-183100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>688700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>168100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>331900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-69200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>318900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>246300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>274300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-13800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>283400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>241800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>201700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-89700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>260300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>206400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>189200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-51900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>247700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>181400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>189100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>269900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,109 +8364,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-64600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-80800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-63500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-69600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-42600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-71000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-59500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-54800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-60800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-101200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-47200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-40400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-25400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-84300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-23900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-26900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-49400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-43600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-39300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8570,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,109 +8674,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-60400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-169800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-80800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-65700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-848700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-42600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-455500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-211800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-54800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-114400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-207100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-47200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-40400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-799400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-23900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-77000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-49500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-27300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-25500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-25300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-65900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-496100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-42700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-174500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-50800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-178700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,109 +8818,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-30100</v>
+        <v>29800</v>
       </c>
       <c r="E96" s="3">
-        <v>-30100</v>
+        <v>30100</v>
       </c>
       <c r="F96" s="3">
-        <v>-29000</v>
+        <v>30100</v>
       </c>
       <c r="G96" s="3">
-        <v>-29200</v>
+        <v>29000</v>
       </c>
       <c r="H96" s="3">
-        <v>-29100</v>
+        <v>29200</v>
       </c>
       <c r="I96" s="3">
-        <v>-29500</v>
+        <v>29100</v>
       </c>
       <c r="J96" s="3">
+        <v>29500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-145600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-36200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-36400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-37200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-143000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-35900</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-36000</v>
       </c>
       <c r="Q96" s="3">
         <v>-36000</v>
       </c>
       <c r="R96" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-33400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-33300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-33100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-33500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-30700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-30600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-31000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-28100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-28500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-29000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-27400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-27700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-24500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9024,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9128,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,307 +9232,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-192800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-229000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>238700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-210700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-488400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>567100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-139300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>72500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-36000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-176100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>203200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-428600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-115700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-192200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>22800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>420400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-166600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-219500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>77300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-187800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-148900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-182400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>129400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>342600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>16200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-108300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>6000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-2700</v>
+        <v>-5600</v>
       </c>
       <c r="E101" s="3">
-        <v>-5000</v>
+        <v>-4300</v>
       </c>
       <c r="F101" s="3">
-        <v>8200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-5600</v>
+        <v>2200</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H101" s="3">
-        <v>-4300</v>
+        <v>-14700</v>
       </c>
       <c r="I101" s="3">
-        <v>2200</v>
+        <v>-12000</v>
       </c>
       <c r="J101" s="3">
+        <v>700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-11100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-14700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-12000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>14400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>9900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>7000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-15000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>5500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-30600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-63100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-227700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>141600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-103600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>172200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-93600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>51100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>103500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-63200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-45700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>65700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>38600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-28500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>51600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>59500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-127200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>52400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>101100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>45900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>24400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>41900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-40700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-27100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>FBHS</t>
   </si>
@@ -656,466 +656,478 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1104200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1155300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1240000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1109600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1161300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1261200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1163700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1040000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4723000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1195500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1255400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1140200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4801100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1986300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1936100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1771000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1659700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1652100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1375800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1402700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1470500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1459000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1507200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1327900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1420700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1380800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1429000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1254600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1382500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1348600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1365400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1186800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1301600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1279000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>571200</v>
+      </c>
+      <c r="E9" s="3">
         <v>625500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>699000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>622000</v>
       </c>
-      <c r="G9" s="3">
-        <v>655600</v>
-      </c>
       <c r="H9" s="3">
+        <v>644700</v>
+      </c>
+      <c r="I9" s="3">
         <v>721100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>695600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>631700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2790100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>716600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>742000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>671800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2840600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1280000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1230300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1126900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1052000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1071500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>892900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>909500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>934600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>934800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>969600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>869100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>920300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>880800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>898900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>814600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>885700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>843200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>850500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>768500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>826400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>798200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>533000</v>
+      </c>
+      <c r="E10" s="3">
         <v>529800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>541000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>487600</v>
       </c>
-      <c r="G10" s="3">
-        <v>505700</v>
-      </c>
       <c r="H10" s="3">
+        <v>516600</v>
+      </c>
+      <c r="I10" s="3">
         <v>540100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>468100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>408300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1932900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>478900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>513400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>468400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1960500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>706300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>705800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>644100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>607700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>580600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>482900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>493200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>535900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>524200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>537600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>458800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>500400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>500000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>530100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>440000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>496800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>505400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>514900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>418300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>475200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>480800</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1152,13 +1164,14 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>69900</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1166,11 +1179,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>64600</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1256,8 +1269,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,216 +1376,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E14" s="3">
         <v>7400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2800</v>
       </c>
-      <c r="G14" s="3">
-        <v>47900</v>
-      </c>
       <c r="H14" s="3">
+        <v>58800</v>
+      </c>
+      <c r="I14" s="3">
         <v>3700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>32400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>20600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>27000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>9300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>23400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>14000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>23000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>35000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>4500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>43400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>38400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>16300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>18100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>6100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E15" s="3">
         <v>19100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>17800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>12600</v>
       </c>
       <c r="J15" s="3">
         <v>12600</v>
       </c>
       <c r="K15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="L15" s="3">
         <v>48300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12500</v>
-      </c>
-      <c r="M15" s="3">
-        <v>11600</v>
       </c>
       <c r="N15" s="3">
         <v>11600</v>
       </c>
       <c r="O15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="P15" s="3">
         <v>46400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>15900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>16000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>10900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>10500</v>
-      </c>
-      <c r="U15" s="3">
-        <v>10300</v>
       </c>
       <c r="V15" s="3">
         <v>10300</v>
       </c>
       <c r="W15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="X15" s="3">
         <v>11400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>9900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>10100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>10000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>10800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>8900</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>8200</v>
       </c>
       <c r="AD15" s="3">
         <v>8200</v>
       </c>
       <c r="AE15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AF15" s="3">
         <v>8100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>7500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>8000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>8100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>7700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,216 +1628,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>910400</v>
+      </c>
+      <c r="E17" s="3">
         <v>942800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1037000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>951400</v>
       </c>
-      <c r="G17" s="3">
-        <v>977900</v>
-      </c>
       <c r="H17" s="3">
+        <v>967000</v>
+      </c>
+      <c r="I17" s="3">
         <v>1061000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>988900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>905100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3948700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1002800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1035900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>960400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3990000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1699700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1641200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1522600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1426500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1411900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1202800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1247700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1278000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1291000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1304800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1192300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1280600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1233700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1240400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1219700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1156200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1071900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1095900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>193800</v>
+      </c>
+      <c r="E18" s="3">
         <v>212500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>203000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>158200</v>
       </c>
-      <c r="G18" s="3">
-        <v>183400</v>
-      </c>
       <c r="H18" s="3">
+        <v>194300</v>
+      </c>
+      <c r="I18" s="3">
         <v>200200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>174800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>134900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>774300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>192700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>219500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>179800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>811100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>286600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>294900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>248400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>233200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>240200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>173000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>155000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>192500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>168000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>202400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>135600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>140100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>147100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>188600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>119400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>162800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>199500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>209200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>114900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>166400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>183100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,528 +1881,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>17200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>12000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>1300</v>
       </c>
       <c r="Q20" s="3">
         <v>1300</v>
       </c>
       <c r="R20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S20" s="3">
         <v>-3300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>6100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-31200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>201200</v>
+      </c>
+      <c r="E21" s="3">
         <v>233200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>225000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>175900</v>
       </c>
-      <c r="G21" s="3">
-        <v>184300</v>
-      </c>
       <c r="H21" s="3">
+        <v>195200</v>
+      </c>
+      <c r="I21" s="3">
         <v>228400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>192600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>153800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>977900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>244100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>266600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>228800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>999800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>334100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>343700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>292800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>279700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>281600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>218300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>198600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>201300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>205000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>241300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>174600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>181300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>194200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>229900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>155700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>189300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>234000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>243700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>147500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>197800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>212400</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E22" s="3">
         <v>30200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>32300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>28600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>27700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>26800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>119200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>33000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>30500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>84300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>21400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>22200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>22400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>24500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>17400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>14700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12900</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>12300</v>
       </c>
       <c r="AG22" s="3">
         <v>12300</v>
       </c>
       <c r="AH22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AI22" s="3">
         <v>11900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>11600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E23" s="3">
         <v>176500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>170500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>125200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>103900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>172600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>130100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>111300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>667100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>162500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>189200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>160200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>726400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>267300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>275000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>223700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>213600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>222200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>156000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>139000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>138900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>144700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>178600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>113100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>117200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>137700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>174600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>107500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>142400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>189400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>199200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>103800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>153200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E24" s="3">
         <v>39900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>36600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>28800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>22600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>36100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>28000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>127200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>44900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>34000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>166700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>65200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>57800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>45900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>47100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>54000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>37800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>29900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>34900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>39000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>41500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>28600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>28700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>40900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>44900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>27000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>40100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>59800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>58900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>26400</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>48800</v>
       </c>
       <c r="AJ24" s="3">
         <v>48800</v>
       </c>
+      <c r="AK24" s="3">
+        <v>48800</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,216 +2521,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E26" s="3">
         <v>136600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>133900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>96400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>81300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>136500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>102100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>85600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>539900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>141400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>144300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>126200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>559700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>202100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>217200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>177800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>166500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>168200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>118200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>109100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>104000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>105700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>137100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>84500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>88500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>96800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>129700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>80500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>102300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>129600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>140300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>77400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>104400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E27" s="3">
         <v>136600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>133900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>96400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>81300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>136500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>102100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>84600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>539900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>141400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>144300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>126200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>559700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>202100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>217200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>177800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>163600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>164600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>115800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>109100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>104100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>105600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>137500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>84700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>88400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>96700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>129600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>80600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>102300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>129500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>140300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>77400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>104300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2842,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2809,31 +2869,31 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-1000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>146800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>62800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>47700</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>54700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>212700</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2841,14 +2901,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -2860,37 +2920,40 @@
         <v>0</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>3100</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>25700</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3056,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,216 +3163,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-17200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-12000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-1300</v>
       </c>
       <c r="Q32" s="3">
         <v>-1300</v>
       </c>
       <c r="R32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="S32" s="3">
         <v>3300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-6100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>31200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>7500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E33" s="3">
         <v>136600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>133900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>96400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>81300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>136500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>102100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>84600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>686700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>204200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>192000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>180900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>772400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>202100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>217200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>177800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>163600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>164600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>115800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>109100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>104100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>105600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>137500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>84700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>85200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>99800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>129600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>75000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>128000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>129500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>137700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>77400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>103600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,221 +3484,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E35" s="3">
         <v>136600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>133900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>96400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>81300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>136500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>102100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>84600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>686700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>204200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>192000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>180900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>772400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>202100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>217200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>177800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>163600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>164600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>115800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>109100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>104100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>105600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>137500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>84700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>85200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>99800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>129600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>75000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>128000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>129500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>137700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>77400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>103600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3744,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,112 +3783,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>381100</v>
+      </c>
+      <c r="E41" s="3">
         <v>344800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>352600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>359700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>366400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>453400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>681700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>539100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>642500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>345300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>360600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>378200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>471500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>460700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>460000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>356100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>419100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>464500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>398400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>359700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>387900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>336200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>276300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>281200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>262900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>389900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>345500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>244400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>323000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>277100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>252700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>210800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>251500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>278600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3826,11 +3915,11 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>73000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3906,424 +3995,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>514400</v>
+      </c>
+      <c r="E43" s="3">
         <v>555900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>593600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>615900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>534200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>578600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>621200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>559000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>521800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>936100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>998500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1011600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>885700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>921800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>844600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>828500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>734900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>765200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>657700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>678200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>624800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>640100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>706200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>650100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>571700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>635400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>657500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>631500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>555300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>594700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>595700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>564900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>550700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>568800</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>960300</v>
+      </c>
+      <c r="E44" s="3">
         <v>962600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>990500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1025200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>982300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>930000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>954500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>931100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1021300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1502300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1446700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1334700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1193800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1128300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1046800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>958400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>867200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>738300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>732300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>703100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>718600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>758800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>741900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>737900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>678900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>684300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>627000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>619200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>580800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>600100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>581400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>558800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>531100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>562500</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>150300</v>
+      </c>
+      <c r="E45" s="3">
         <v>153400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>142700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>145400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>135900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>184700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>183900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>196300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>274800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>223900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>258000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>232200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>193500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>215200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>197500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>202900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>187300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>170000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>168900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>173000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>166900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>171600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>192500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>178800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>172600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>180600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>175500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>149400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>142600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>126400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>123300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>121600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>111900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>129800</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2007400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2019100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2081900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2172100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2045700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2149700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2443600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2301200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2460400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3007600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3063800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2956700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2744500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2726000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2548900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2345900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2208500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2138000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1957300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1914000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1898200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1906700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1916900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1848000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1686100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1890200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1805500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1644500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1601700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1598300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1553100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1456100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1445200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1539700</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4336,8 +4440,8 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
-        <v>3500</v>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>8</v>
@@ -4348,8 +4452,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4426,216 +4530,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1147300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1138300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1140000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1153200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1148800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1052400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>980700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>917700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>902600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1274700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1266800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1248300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1201200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1134100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1107400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1084300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1087600</v>
-      </c>
-      <c r="T48" s="3">
-        <v>958600</v>
       </c>
       <c r="U48" s="3">
         <v>958600</v>
       </c>
       <c r="V48" s="3">
+        <v>958600</v>
+      </c>
+      <c r="W48" s="3">
         <v>966900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>989800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>966200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>978100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>981100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>813400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>776300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>737600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>742800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>740000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>690600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>675600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>665700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>662500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>642900</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3289200</v>
+      </c>
+      <c r="E49" s="3">
         <v>3329000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3331000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3343400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3261500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3304200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3332200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2634300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2641500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3922100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3814200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3870000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3848900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3867900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3891200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3900500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3815100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3196400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3199300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3219200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3259100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3271000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3314900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3323700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3327100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3397100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3055700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3069900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3074400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2958200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2925300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2930100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2940800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2948900</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4851,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,112 +4958,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>98500</v>
+      </c>
+      <c r="E52" s="3">
         <v>112000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>121000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>122800</v>
       </c>
-      <c r="G52" s="3">
-        <v>87000</v>
-      </c>
       <c r="H52" s="3">
+        <v>90500</v>
+      </c>
+      <c r="I52" s="3">
         <v>111800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>116700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>119500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>116400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>211200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>189300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>168000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>141600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>140800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>148500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>151400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>247500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>226000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>217100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>200000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>144200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>141700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>133500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>136400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>138000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>106100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>98300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>94800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>95300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>102200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>99400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>82200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>80000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,112 +5172,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6561800</v>
+      </c>
+      <c r="E54" s="3">
         <v>6598400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6673900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6791500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6565000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6618100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6873200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5972700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6120900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8415600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8334100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8243000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7936200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7868800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7696000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7482100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7358700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6519000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6332300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6300100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6291300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6285600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6343400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6289200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5964600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6169700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5697100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5552000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5511400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5349300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5253400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5134100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5128500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5212600</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5320,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,153 +5359,157 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>513900</v>
+      </c>
+      <c r="E57" s="3">
         <v>493300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>554400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>571400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>568100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>570400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>489500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>423700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>421600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>672600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>756300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>728100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>764900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>735700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>697500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>599200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>620500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>544100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>463900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>426400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>460000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>436500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>476600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>442000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>459000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>437700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>428700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>417100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>428800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>392500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>397000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>378900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>393800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>361900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>531100</v>
+      </c>
+      <c r="E58" s="3">
         <v>499500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>499300</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
-        <v>37100</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>599800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>599500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>599200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>600300</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>400000</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
@@ -5384,8 +5517,8 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5394,34 +5527,34 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>399900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>399700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>399500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>749300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>350000</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>525000</v>
       </c>
       <c r="AB58" s="3">
         <v>525000</v>
       </c>
       <c r="AC58" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="AD58" s="3">
         <v>350000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
+      <c r="AE58" s="3">
+        <v>350000</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
@@ -5432,430 +5565,445 @@
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E59" s="3">
         <v>539400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>494300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>491100</v>
       </c>
-      <c r="G59" s="3">
-        <v>248600</v>
-      </c>
       <c r="H59" s="3">
+        <v>61800</v>
+      </c>
+      <c r="I59" s="3">
         <v>621700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>551400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>390000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>523900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>775000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>685200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>626700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>806200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>793100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>667200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>597800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>724600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>590900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>488900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>419800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>549600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>540600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>469300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>446800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>508100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>488900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>451800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>373700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>478000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>460000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>394100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>328900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>449000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1602300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1532200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1548000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1062500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1200400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1192100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1640700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1413200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1544700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2047900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1441500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1354800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1971100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1528800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1364700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1197000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1345100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1135000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>952800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1246100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1409300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1376600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1695200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1238800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1492100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1451600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1230500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1140800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>906800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>852500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>791100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>707800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>842800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>776700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2295300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2405600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2536000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3185200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2813400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2921400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2757500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2164900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2074300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2786900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3357900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3367900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2309800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2629100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2608300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2682800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2572200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2086500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2245900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2035200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1784600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1949000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1666000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2169700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1809000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1988400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1793300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1538000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1507600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1462200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1391900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1491500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1431100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1585800</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E62" s="3">
         <v>85900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>86200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>89200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>99200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>100400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>93600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>102400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>415000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>550700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>582300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>605500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>590500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>656300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>679500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>677900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>665900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>668900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>670500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>660900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>669600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>623300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>637500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>633600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>483500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>496100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>498600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>514900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>495900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>488700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>501700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>504100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>491600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>489900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6106,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6213,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,112 +6320,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4139800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4202500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4343300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4510700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4271600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4399100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4696100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3890200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4034000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5385500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5381700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5328200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4871400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4814200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4652500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4557700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4583200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3890400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3870500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3943100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3864700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3950200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3999900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4043700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3786400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3937800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3524000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3195200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2911900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2805000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2686200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2704900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2767000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2853800</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6468,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6573,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6680,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6787,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,112 +6894,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2956800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2882500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2805500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2701800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2605300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2554200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2475400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2402400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2323800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3277000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3145000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2989400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2807900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2670000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2539300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2358000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2180200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2052700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1954700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1872100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1763000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1692500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1648100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1541400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1448100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1393400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1350500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1249900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1076500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1002000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>892000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>814600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7108,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7215,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,112 +7322,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2422000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2395900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2330600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2280800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2293400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2219000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2177100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2082500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2086900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3030100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2952400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2914800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3064800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3054600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3043500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2924400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2775500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2628600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2461800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2357000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2426600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2335400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2343500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2245500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2178200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2231900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2173100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2356800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2599500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2544300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2567200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2429200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2361500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2358800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,221 +7536,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E81" s="3">
         <v>136600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>133900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>96400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>81300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>136500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>102100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>84600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>686700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>204200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>192000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>180900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>772400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>202100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>217200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>177800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>163600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>164600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>115800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>109100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>104100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>105600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>137500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>84700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>85200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>99800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>129600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>75000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>128000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>129500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>137700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>77400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>103600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,112 +7796,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E83" s="3">
         <v>26600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19300</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>30800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>30900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>191600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>48600</v>
-      </c>
-      <c r="M83" s="3">
-        <v>46900</v>
       </c>
       <c r="N83" s="3">
         <v>46900</v>
       </c>
       <c r="O83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="P83" s="3">
         <v>189100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>46200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>47500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>47700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>46600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>39300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>40100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>37500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>40000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>36700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>38200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>37800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>40700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>37500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>37900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>33500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>34000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>32300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>32200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>31800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>33000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8008,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8115,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8222,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8329,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,112 +8436,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>272300</v>
+      </c>
+      <c r="E89" s="3">
         <v>205300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>261500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-71300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>220200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>332000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>427500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>76100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>566300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>246900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>225000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-183100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>688700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>168100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>331900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-69200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>318900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>246300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>274300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-13800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>283400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>241800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>201700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-89700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>260300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>206400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>189200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-51900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>247700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>181400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>189100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>269900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,112 +8584,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-60200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-29700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-38800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-64600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-80800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-63500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-69600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-54800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-60800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-101200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-47200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-40400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-25400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-84300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-23900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-49400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-43600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-39300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +8796,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,112 +8903,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-44200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-28500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-60400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-169800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-80800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-65700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-848700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-42600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-455500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-211800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-114400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-207100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-47200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-40400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-799400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-23200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-77000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-49500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-27300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-25500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-25300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-65900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-496100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-42700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-174500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-50800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-178700</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,112 +9051,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E96" s="3">
         <v>29800</v>
-      </c>
-      <c r="E96" s="3">
-        <v>30100</v>
       </c>
       <c r="F96" s="3">
         <v>30100</v>
       </c>
       <c r="G96" s="3">
+        <v>30100</v>
+      </c>
+      <c r="H96" s="3">
         <v>29000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>29200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>29100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>29500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-145600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-36200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-36400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-37200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-143000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-35900</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-36000</v>
       </c>
       <c r="R96" s="3">
         <v>-36000</v>
       </c>
       <c r="S96" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-33400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-33300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-33100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-33500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-30700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-30600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-30700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-31000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-28100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-28500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-29000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-27400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-27700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-24500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9263,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9370,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,316 +9477,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-180300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-192800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-229000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>238700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-210700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-488400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>567100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-139300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>72500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-36000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-176100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>203200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-428600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-115700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-192200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>22800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>420400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-166600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-219500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>77300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-187800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-148900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-182400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>129400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>342600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>16200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-108300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>6000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2200</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-14700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-14700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-12000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>14400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>9900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-15000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>5500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>6400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-63100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-227700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>141600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-103600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>172200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-93600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>51100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>103500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-63200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-45700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>65700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>38600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-28500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>51600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>59500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>18200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-127200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>52400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>101100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>45900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>24400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>41900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-40700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-27100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
   <si>
     <t>FBHS</t>
   </si>
@@ -656,478 +656,491 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1033100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1104200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1155300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1240000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1109600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1161300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1261200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1163700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1040000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4723000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1195500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1255400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1140200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4801100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1986300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1936100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1771000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1659700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1652100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1375800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1402700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1470500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1459000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1507200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1327900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1420700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1380800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1429000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1254600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1382500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1348600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1365400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1186800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1301600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1279000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>578400</v>
+      </c>
+      <c r="E9" s="3">
         <v>571200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>625500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>699000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>622000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>644700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>721100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>695600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>631700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2790100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>716600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>742000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>671800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2840600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1280000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1230300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1126900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1052000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1071500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>892900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>909500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>934600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>934800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>969600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>869100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>920300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>880800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>898900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>814600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>885700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>843200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>850500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>768500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>826400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>798200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>454700</v>
+      </c>
+      <c r="E10" s="3">
         <v>533000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>529800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>541000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>487600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>516600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>540100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>468100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>408300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1932900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>478900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>513400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>468400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1960500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>706300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>705800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>644100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>607700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>580600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>482900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>493200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>535900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>524200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>537600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>458800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>500400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>500000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>530100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>440000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>496800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>505400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>514900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>418300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>475200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>480800</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1165,16 +1178,17 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>69900</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1182,11 +1196,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>64600</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1272,8 +1286,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1379,222 +1396,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E14" s="3">
         <v>27200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>58800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>22200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>32400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>20600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>27000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>23400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>14000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>23000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>35000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>43400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>38400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>16300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>18100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>2600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E15" s="3">
         <v>17900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>17800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>12600</v>
       </c>
       <c r="K15" s="3">
         <v>12600</v>
       </c>
       <c r="L15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="M15" s="3">
         <v>48300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12500</v>
-      </c>
-      <c r="N15" s="3">
-        <v>11600</v>
       </c>
       <c r="O15" s="3">
         <v>11600</v>
       </c>
       <c r="P15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="Q15" s="3">
         <v>46400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>15900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>16000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>10900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>10500</v>
-      </c>
-      <c r="V15" s="3">
-        <v>10300</v>
       </c>
       <c r="W15" s="3">
         <v>10300</v>
       </c>
       <c r="X15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="Y15" s="3">
         <v>11400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>9900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>10100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>10000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>10800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>8900</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>8200</v>
       </c>
       <c r="AE15" s="3">
         <v>8200</v>
       </c>
       <c r="AF15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AG15" s="3">
         <v>8100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>7500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>8000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>7700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1629,222 +1655,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>911300</v>
+      </c>
+      <c r="E17" s="3">
         <v>910400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>942800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1037000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>951400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>967000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1061000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>988900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>905100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3948700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1002800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1035900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>960400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3990000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1699700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1641200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1522600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1426500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1411900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1202800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1247700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1278000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1291000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1304800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1192300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1280600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1233700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1240400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1219700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1156200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1071900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1095900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>121800</v>
+      </c>
+      <c r="E18" s="3">
         <v>193800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>212500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>203000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>158200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>194300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>200200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>174800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>134900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>774300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>192700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>219500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>179800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>811100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>286600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>294900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>248400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>233200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>240200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>173000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>155000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>192500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>168000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>202400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>135600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>140100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>147100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>188600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>119400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>162800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>199500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>209200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>114900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>166400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>183100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1882,543 +1915,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>10500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>17200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-6300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>12000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-400</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>1300</v>
       </c>
       <c r="R20" s="3">
         <v>1300</v>
       </c>
       <c r="S20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T20" s="3">
         <v>-3300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>9600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>140800</v>
+      </c>
+      <c r="E21" s="3">
         <v>201200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>233200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>225000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>175900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>195200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>228400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>192600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>153800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>977900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>244100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>266600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>228800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>999800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>334100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>343700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>292800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>279700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>281600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>218300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>198600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>201300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>205000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>241300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>174600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>181300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>194200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>229900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>155700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>189300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>234000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>243700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>147500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>197800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>212400</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E22" s="3">
         <v>27900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>32300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>30100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>28600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>27700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>26800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>119200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>33000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>30500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>84300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>21200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>22100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>22400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>24500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>19000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>17400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>14700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12900</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>12300</v>
       </c>
       <c r="AH22" s="3">
         <v>12300</v>
       </c>
       <c r="AI22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>11600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E23" s="3">
         <v>133300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>176500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>170500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>125200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>103900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>172600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>130100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>111300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>667100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>162500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>189200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>160200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>726400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>267300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>275000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>223700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>213600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>222200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>156000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>139000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>138900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>144700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>178600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>113100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>117200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>137700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>174600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>107500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>142400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>189400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>199200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>103800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>153200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E24" s="3">
         <v>28200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>36600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>22600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>36100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>127200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>44900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>34000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>166700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>65200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>57800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>45900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>47100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>54000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>37800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>29900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>34900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>39000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>41500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>28600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>28700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>40900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>44900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>27000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>40100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>59800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>58900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>26400</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>48800</v>
       </c>
       <c r="AK24" s="3">
         <v>48800</v>
       </c>
+      <c r="AL24" s="3">
+        <v>48800</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2524,222 +2573,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E26" s="3">
         <v>105100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>136600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>133900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>96400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>81300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>136500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>102100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>85600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>539900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>141400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>144300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>126200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>559700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>202100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>217200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>177800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>166500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>168200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>118200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>109100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>104000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>105700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>137100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>84500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>88500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>96800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>129700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>80500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>102300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>129600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>140300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>77400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>104400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E27" s="3">
         <v>105100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>136600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>133900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>96400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>81300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>136500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>102100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>84600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>539900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>141400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>144300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>126200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>559700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>202100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>217200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>177800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>163600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>164600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>115800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>109100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>104100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>105600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>137500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>84700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>88400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>96700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>129600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>80600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>102300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>129500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>140300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>77400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>104300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2845,8 +2903,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2872,31 +2933,31 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-1000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>146800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>62800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>47700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>54700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>212700</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -2904,14 +2965,14 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
@@ -2923,37 +2984,40 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>3100</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>25700</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI29" s="3" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-700</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3059,8 +3123,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3166,222 +3233,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-17200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>6300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-12000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>400</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-1300</v>
       </c>
       <c r="R32" s="3">
         <v>-1300</v>
       </c>
       <c r="S32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="T32" s="3">
         <v>3300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>31200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>7500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E33" s="3">
         <v>105100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>136600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>133900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>96400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>81300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>136500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>102100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>84600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>686700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>204200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>192000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>180900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>772400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>202100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>217200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>177800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>163600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>164600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>115800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>109100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>104100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>105600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>137500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>84700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>85200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>99800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>129600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>75000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>128000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>129500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>137700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>77400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>103600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3487,227 +3563,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E35" s="3">
         <v>105100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>136600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>133900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>96400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>81300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>136500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>102100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>84600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>686700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>204200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>192000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>180900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>772400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>202100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>217200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>177800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>163600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>164600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>115800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>109100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>104100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>105600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>137500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>84700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>85200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>99800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>129600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>75000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>128000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>129500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>137700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>77400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>103600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3745,8 +3830,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3784,115 +3870,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>340000</v>
+      </c>
+      <c r="E41" s="3">
         <v>381100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>344800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>352600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>359700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>366400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>453400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>681700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>539100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>642500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>345300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>360600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>378200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>471500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>460700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>460000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>356100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>419100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>464500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>398400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>359700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>387900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>336200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>276300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>281200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>262900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>389900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>345500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>244400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>323000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>277100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>252700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>210800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>251500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>278600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3918,11 +4008,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>73000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3998,436 +4088,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>563700</v>
+      </c>
+      <c r="E43" s="3">
         <v>514400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>555900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>593600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>615900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>534200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>578600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>621200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>559000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>521800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>936100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>998500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1011600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>885700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>921800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>844600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>828500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>734900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>765200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>657700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>678200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>624800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>640100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>706200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>650100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>571700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>635400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>657500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>631500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>555300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>594700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>595700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>564900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>550700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>568800</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1003500</v>
+      </c>
+      <c r="E44" s="3">
         <v>960300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>962600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>990500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1025200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>982300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>930000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>954500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>931100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1021300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1502300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1446700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1334700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1193800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1128300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1046800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>958400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>867200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>738300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>732300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>703100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>718600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>758800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>741900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>737900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>678900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>684300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>627000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>619200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>580800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>600100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>581400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>558800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>531100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>562500</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>153500</v>
+      </c>
+      <c r="E45" s="3">
         <v>150300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>153400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>142700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>145400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>135900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>184700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>183900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>196300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>274800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>223900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>258000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>232200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>193500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>215200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>197500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>202900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>187300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>170000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>168900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>173000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>166900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>171600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>192500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>178800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>172600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>180600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>175500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>149400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>142600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>126400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>123300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>121600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>111900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>129800</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2062000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2007400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2019100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2081900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2172100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2045700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2149700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2443600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2301200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2460400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3007600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3063800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2956700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2744500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2726000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2548900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2345900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2208500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2138000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1957300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1914000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1898200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1906700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1916900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1848000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1686100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1890200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1805500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1644500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1601700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1598300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1553100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1456100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1445200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1539700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4455,8 +4560,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4533,222 +4638,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1132100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1147300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1138300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1140000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1153200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1148800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1052400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>980700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>917700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>902600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1274700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1266800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1248300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1201200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1134100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1107400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1084300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1087600</v>
-      </c>
-      <c r="U48" s="3">
-        <v>958600</v>
       </c>
       <c r="V48" s="3">
         <v>958600</v>
       </c>
       <c r="W48" s="3">
+        <v>958600</v>
+      </c>
+      <c r="X48" s="3">
         <v>966900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>989800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>966200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>978100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>981100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>813400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>776300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>737600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>742800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>740000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>690600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>675600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>665700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>662500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>642900</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3278100</v>
+      </c>
+      <c r="E49" s="3">
         <v>3289200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3329000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3331000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3343400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3261500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3304200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3332200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2634300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2641500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3922100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3814200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3870000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3848900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3867900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3891200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3900500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3815100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3196400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3199300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3219200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3259100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3271000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3314900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3323700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3327100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3397100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3055700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3069900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3074400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2958200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2925300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2930100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2940800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2948900</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4854,8 +4968,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4961,115 +5078,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>112600</v>
+      </c>
+      <c r="E52" s="3">
         <v>98500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>112000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>121000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>122800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>90500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>111800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>116700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>119500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>116400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>211200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>189300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>168000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>141600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>140800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>148500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>151400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>247500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>226000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>217100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>200000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>144200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>141700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>133500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>136400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>138000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>106100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>98300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>94800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>95300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>102200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>99400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>82200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>80000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5175,115 +5298,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6584800</v>
+      </c>
+      <c r="E54" s="3">
         <v>6561800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6598400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6673900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6791500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6565000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6618100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6873200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5972700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6120900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8415600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8334100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8243000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7936200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7868800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7696000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7482100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7358700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6519000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6332300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6300100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6291300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6285600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6343400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6289200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5964600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6169700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5697100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5552000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5511400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5349300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5253400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5134100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5128500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5212600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5321,8 +5450,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5360,130 +5490,134 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>519700</v>
+      </c>
+      <c r="E57" s="3">
         <v>513900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>493300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>554400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>571400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>568100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>570400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>489500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>423700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>421600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>672600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>756300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>728100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>764900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>735700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>697500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>599200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>620500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>544100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>463900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>426400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>460000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>436500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>476600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>442000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>459000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>437700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>428700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>417100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>428800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>392500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>397000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>378900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>393800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>361900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>499800</v>
+      </c>
+      <c r="E58" s="3">
         <v>531100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>499500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>499300</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -5491,28 +5625,28 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>599800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>599500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>599200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>600300</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>400000</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
@@ -5520,8 +5654,8 @@
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5530,34 +5664,34 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>399900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>399700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>399500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>749300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>350000</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>525000</v>
       </c>
       <c r="AC58" s="3">
         <v>525000</v>
       </c>
       <c r="AD58" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="AE58" s="3">
         <v>350000</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
+      <c r="AF58" s="3">
+        <v>350000</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
@@ -5568,442 +5702,457 @@
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>442400</v>
+      </c>
+      <c r="E59" s="3">
         <v>57600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>539400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>494300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>491100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>61800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>621700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>551400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>390000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>523900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>775000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>685200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>626700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>806200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>793100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>667200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>597800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>724600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>590900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>488900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>419800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>549600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>540600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>469300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>446800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>508100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>488900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>451800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>373700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>478000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>460000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>394100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>328900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>449000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1461900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1602300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1532200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1548000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1062500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1200400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1192100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1640700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1413200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1544700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2047900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1441500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1354800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1971100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1528800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1364700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1197000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1345100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1135000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>952800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1246100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1409300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1376600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1695200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1238800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1492100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1451600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1230500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1140800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>906800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>852500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>791100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>707800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>842800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>776700</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2569600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2295300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2405600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2536000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3185200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2813400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2921400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2757500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2164900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2074300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2786900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3357900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3367900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2309800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2629100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2608300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2682800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2572200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2086500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2245900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2035200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1784600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1949000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1666000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2169700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1809000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1988400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1793300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1538000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1507600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1462200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1391900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1491500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1431100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1585800</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E62" s="3">
         <v>92300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>85900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>86200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>89200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>99200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>100400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>93600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>102400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>415000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>550700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>582300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>605500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>590500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>656300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>679500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>677900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>665900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>668900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>670500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>660900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>669600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>623300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>637500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>633600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>483500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>496100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>498600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>514900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>495900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>488700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>501700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>504100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>491600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>489900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6109,8 +6258,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6216,8 +6368,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6323,115 +6478,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4280200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4139800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4202500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4343300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4510700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4271600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4399100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4696100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3890200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4034000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5385500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5381700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5328200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4871400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4814200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4652500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4557700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4583200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3890400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3870500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3943100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3864700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3950200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3999900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4043700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3786400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3937800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3524000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3195200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2911900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2805000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2686200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2704900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2767000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2853800</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6469,8 +6630,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6576,8 +6738,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6683,8 +6848,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6790,8 +6958,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6897,115 +7068,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3008600</v>
+      </c>
+      <c r="E72" s="3">
         <v>2956800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2882500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2805500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2701800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2605300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2554200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2475400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2402400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2323800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3277000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3145000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2989400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2807900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2670000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2539300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2358000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2180200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2052700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1954700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1872100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1763000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1692500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1648100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1541400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1448100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1393400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1350500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1249900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1076500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1002000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>892000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>814600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7111,8 +7288,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7218,8 +7398,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7325,115 +7508,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2304600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2422000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2395900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2330600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2280800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2293400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2219000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2177100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2082500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2086900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3030100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2952400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2914800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3064800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3054600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3043500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2924400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2775500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2628600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2461800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2357000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2426600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2335400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2343500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2245500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2178200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2231900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2173100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2356800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2599500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2544300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2567200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2429200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2361500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2358800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7539,227 +7728,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E81" s="3">
         <v>105100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>136600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>133900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>96400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>81300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>136500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>102100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>84600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>686700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>204200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>192000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>180900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>772400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>202100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>217200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>177800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>163600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>164600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>115800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>109100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>104100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>105600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>137500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>84700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>85200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>99800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>129600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>75000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>128000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>129500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>137700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>77400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>103600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7797,115 +7995,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E83" s="3">
         <v>39200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19300</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="I83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>30800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>191600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>48600</v>
-      </c>
-      <c r="N83" s="3">
-        <v>46900</v>
       </c>
       <c r="O83" s="3">
         <v>46900</v>
       </c>
       <c r="P83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="Q83" s="3">
         <v>189100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>46200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>47500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>47700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>46600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>39300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>40100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>37500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>40000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>36700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>38200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>37800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>40700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>37500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>37900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>33500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>34000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>32300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>32200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>31800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>33000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8011,8 +8213,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8118,8 +8323,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8225,8 +8433,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8332,8 +8543,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8439,115 +8653,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-83400</v>
+      </c>
+      <c r="E89" s="3">
         <v>272300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>205300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>261500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-71300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>220200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>332000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>427500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>76100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>566300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>246900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>225000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-183100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>688700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>168100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>331900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-69200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>318900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>246300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>274300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-13800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>283400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>241800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>201700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-89700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>260300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>206400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>189200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-51900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>247700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>181400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>189100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>269900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8585,115 +8805,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-60200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-29700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-64600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-80800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-63500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-69600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-42600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-71000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-59500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-54800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-60800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-101200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-47200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-40400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-25400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-84300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-23900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-49400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-27200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-43600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-39300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8799,8 +9023,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8906,115 +9133,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-44200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-60400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-169800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-80800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-65700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-848700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-42600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-455500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-211800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-114400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-207100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-47200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-40400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-18500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-799400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-23900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-77000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-25300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-65900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-496100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-42700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-174500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-50800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-178700</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9052,115 +9285,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E96" s="3">
         <v>29600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>29800</v>
-      </c>
-      <c r="F96" s="3">
-        <v>30100</v>
       </c>
       <c r="G96" s="3">
         <v>30100</v>
       </c>
       <c r="H96" s="3">
+        <v>30100</v>
+      </c>
+      <c r="I96" s="3">
         <v>29000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>29200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>29100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>29500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-145600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-36200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-36400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-37200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-143000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-35900</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-36000</v>
       </c>
       <c r="S96" s="3">
         <v>-36000</v>
       </c>
       <c r="T96" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-33400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-33300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-33100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-33500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-30700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-30600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-30700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-31000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-28100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-28500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-29000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-27400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-27700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-24500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9266,8 +9503,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9373,8 +9613,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9480,325 +9723,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-180300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-192800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-229000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>238700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-210700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-488400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>567100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-139300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>72500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-36000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-176100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>203200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-428600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-115700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-192200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>22800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>420400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-166600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-219500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>77300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-187800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-148900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-182400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>129400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>342600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>16200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-108300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>8200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2200</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="I101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-14700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-12000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>14400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>9900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-15000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="E102" s="3">
         <v>35500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-63100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-227700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>141600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-103600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>172200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-93600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>51100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>103500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-63200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-45700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>65700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>38600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-28500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>51600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>59500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>18200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-127200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>52400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>101100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>45900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>24400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>41900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-40700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-27100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>FBHS</t>
   </si>
@@ -656,491 +656,504 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1203300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1033100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1104200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1155300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1240000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1109600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1161300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1261200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1163700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1040000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4723000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1195500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1255400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1140200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4801100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1986300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1936100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1771000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1659700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1652100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1375800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1402700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1470500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1459000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1507200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1327900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1420700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1380800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1429000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1254600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1382500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1348600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1365400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1186800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1301600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1279000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>659500</v>
+      </c>
+      <c r="E9" s="3">
         <v>578400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>571200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>625500</v>
       </c>
-      <c r="G9" s="3">
-        <v>699000</v>
-      </c>
       <c r="H9" s="3">
+        <v>687000</v>
+      </c>
+      <c r="I9" s="3">
         <v>622000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>644700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>721100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>695600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>631700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2790100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>716600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>742000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>671800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2840600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1280000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1230300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1126900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1052000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1071500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>892900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>909500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>934600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>934800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>969600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>869100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>920300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>880800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>898900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>814600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>885700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>843200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>850500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>768500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>826400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>798200</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>543800</v>
+      </c>
+      <c r="E10" s="3">
         <v>454700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>533000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>529800</v>
       </c>
-      <c r="G10" s="3">
-        <v>541000</v>
-      </c>
       <c r="H10" s="3">
+        <v>553000</v>
+      </c>
+      <c r="I10" s="3">
         <v>487600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>516600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>540100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>468100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>408300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1932900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>478900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>513400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>468400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1960500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>706300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>705800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>644100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>607700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>580600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>482900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>493200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>535900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>524200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>537600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>458800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>500400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>500000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>530100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>440000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>496800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>505400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>514900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>418300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>475200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>480800</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1179,19 +1192,20 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>69900</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1199,11 +1213,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>64600</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1289,8 +1303,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1399,228 +1416,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E14" s="3">
         <v>24800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>27200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7400</v>
       </c>
-      <c r="G14" s="3">
-        <v>3900</v>
-      </c>
       <c r="H14" s="3">
+        <v>15900</v>
+      </c>
+      <c r="I14" s="3">
         <v>2800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>58800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>22200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>32400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>20600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>27000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>23400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>23000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>35000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>43400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>38400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>16300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>18100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>6100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>2600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E15" s="3">
         <v>18000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>18800</v>
-      </c>
-      <c r="K15" s="3">
-        <v>12600</v>
       </c>
       <c r="L15" s="3">
         <v>12600</v>
       </c>
       <c r="M15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="N15" s="3">
         <v>48300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12500</v>
-      </c>
-      <c r="O15" s="3">
-        <v>11600</v>
       </c>
       <c r="P15" s="3">
         <v>11600</v>
       </c>
       <c r="Q15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="R15" s="3">
         <v>46400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>15900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>16000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>16600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>10900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>10500</v>
-      </c>
-      <c r="W15" s="3">
-        <v>10300</v>
       </c>
       <c r="X15" s="3">
         <v>10300</v>
       </c>
       <c r="Y15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="Z15" s="3">
         <v>11400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>9900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>10100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>10000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>10800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>8900</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>8200</v>
       </c>
       <c r="AF15" s="3">
         <v>8200</v>
       </c>
       <c r="AG15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AH15" s="3">
         <v>8100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>7500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>8100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>7700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1656,228 +1682,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1004400</v>
+      </c>
+      <c r="E17" s="3">
         <v>911300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>910400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>942800</v>
       </c>
-      <c r="G17" s="3">
-        <v>1037000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1022900</v>
+      </c>
+      <c r="I17" s="3">
         <v>951400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>967000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1061000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>988900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>905100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3948700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1002800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1035900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>960400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3990000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1699700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1641200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1522600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1426500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1411900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1202800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1247700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1278000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1291000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1304800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1192300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1280600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1233700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1240400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1219700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1156200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1071900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1095900</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>198900</v>
+      </c>
+      <c r="E18" s="3">
         <v>121800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>193800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>212500</v>
       </c>
-      <c r="G18" s="3">
-        <v>203000</v>
-      </c>
       <c r="H18" s="3">
+        <v>217100</v>
+      </c>
+      <c r="I18" s="3">
         <v>158200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>194300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>200200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>174800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>134900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>774300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>192700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>219500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>179800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>811100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>286600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>294900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>248400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>233200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>240200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>173000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>155000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>192500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>168000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>202400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>135600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>140100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>147100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>188600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>119400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>162800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>199500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>209200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>114900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>166400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>183100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1916,558 +1949,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3700</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>17200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-6300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>1300</v>
       </c>
       <c r="S20" s="3">
         <v>1300</v>
       </c>
       <c r="T20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U20" s="3">
         <v>-3300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>9600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>225400</v>
+      </c>
+      <c r="E21" s="3">
         <v>140800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>201200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>233200</v>
       </c>
-      <c r="G21" s="3">
-        <v>225000</v>
-      </c>
       <c r="H21" s="3">
+        <v>237000</v>
+      </c>
+      <c r="I21" s="3">
         <v>175900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>195200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>228400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>192600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>153800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>977900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>244100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>266600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>228800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>999800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>334100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>343700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>292800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>279700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>281600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>218300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>198600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>201300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>205000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>241300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>174600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>181300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>194200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>229900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>155700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>189300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>234000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>243700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>147500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>197800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>212400</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E22" s="3">
         <v>28600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>32300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>30100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>28600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>33300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>27700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>26800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>119200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>33000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>30500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>84300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>21400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>20100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>22200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>22100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>22400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>24500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>23400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>19000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>17400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>14700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>12900</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>12300</v>
       </c>
       <c r="AI22" s="3">
         <v>12300</v>
       </c>
       <c r="AJ22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AK22" s="3">
         <v>11900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>11600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>147700</v>
+      </c>
+      <c r="E23" s="3">
         <v>69400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>133300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>176500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>170500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>125200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>103900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>172600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>130100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>111300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>667100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>162500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>189200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>160200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>726400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>267300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>275000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>223700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>213600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>222200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>156000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>139000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>138900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>144700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>178600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>113100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>117200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>137700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>174600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>107500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>142400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>189400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>199200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>103800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>153200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E24" s="3">
         <v>18000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>36600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>22600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>36100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>25700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>127200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>21100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>44900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>34000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>166700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>65200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>57800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>45900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>47100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>54000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>37800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>29900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>34900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>39000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>41500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>28600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>28700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>40900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>44900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>27000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>40100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>59800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>58900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>26400</v>
-      </c>
-      <c r="AK24" s="3">
-        <v>48800</v>
       </c>
       <c r="AL24" s="3">
         <v>48800</v>
       </c>
+      <c r="AM24" s="3">
+        <v>48800</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2576,228 +2625,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E26" s="3">
         <v>51400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>105100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>136600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>133900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>96400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>81300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>136500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>102100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>85600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>539900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>141400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>144300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>126200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>559700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>202100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>217200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>177800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>166500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>168200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>118200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>109100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>104000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>105700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>137100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>84500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>88500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>96800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>129700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>80500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>102300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>129600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>140300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>77400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>104400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E27" s="3">
         <v>51400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>105100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>136600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>133900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>96400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>81300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>136500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>102100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>84600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>539900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>141400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>144300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>126200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>559700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>202100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>217200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>177800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>163600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>164600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>115800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>109100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>104100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>105600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>137500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>84700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>88400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>96700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>129600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>80600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>102300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>129500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>140300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>77400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>104300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2906,8 +2964,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2936,31 +2997,31 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-1000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>146800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>62800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>47700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>54700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>212700</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2968,14 +3029,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2987,37 +3048,40 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>3100</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>25700</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-700</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3126,8 +3190,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3236,228 +3303,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
-        <v>3700</v>
-      </c>
       <c r="H32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-17200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>6300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-1300</v>
       </c>
       <c r="S32" s="3">
         <v>-1300</v>
       </c>
       <c r="T32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="U32" s="3">
         <v>3300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>31200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>7500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E33" s="3">
         <v>51400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>105100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>136600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>133900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>96400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>81300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>136500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>102100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>84600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>686700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>204200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>192000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>180900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>772400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>202100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>217200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>177800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>163600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>164600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>115800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>109100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>104100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>105600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>137500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>84700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>85200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>99800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>129600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>75000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>128000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>129500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>137700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>77400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>103600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3566,233 +3642,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E35" s="3">
         <v>51400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>105100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>136600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>133900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>96400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>81300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>136500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>102100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>84600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>686700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>204200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>192000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>180900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>772400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>202100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>217200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>177800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>163600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>164600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>115800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>109100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>104100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>105600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>137500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>84700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>85200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>99800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>129600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>75000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>128000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>129500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>137700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>77400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>103600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3831,8 +3916,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3871,118 +3957,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>234700</v>
+      </c>
+      <c r="E41" s="3">
         <v>340000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>381100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>344800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>352600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>359700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>366400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>453400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>681700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>539100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>642500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>345300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>360600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>378200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>471500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>460700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>460000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>356100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>419100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>464500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>398400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>359700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>387900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>336200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>276300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>281200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>262900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>389900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>345500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>244400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>323000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>277100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>252700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>210800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>251500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>278600</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4011,11 +4101,11 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>73000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4091,448 +4181,463 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>607100</v>
+      </c>
+      <c r="E43" s="3">
         <v>563700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>514400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>555900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>593600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>615900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>534200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>578600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>621200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>559000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>521800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>936100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>998500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1011600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>885700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>921800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>844600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>828500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>734900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>765200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>657700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>678200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>624800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>640100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>706200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>650100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>571700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>635400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>657500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>631500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>555300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>594700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>595700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>564900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>550700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>568800</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1012700</v>
+      </c>
+      <c r="E44" s="3">
         <v>1003500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>960300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>962600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>990500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1025200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>982300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>930000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>954500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>931100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1021300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1502300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1446700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1334700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1193800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1128300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1046800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>958400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>867200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>738300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>732300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>703100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>718600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>758800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>741900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>737900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>678900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>684300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>627000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>619200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>580800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>600100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>581400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>558800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>531100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>562500</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>150800</v>
+      </c>
+      <c r="E45" s="3">
         <v>153500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>150300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>153400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>142700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>145400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>135900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>184700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>183900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>196300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>274800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>223900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>258000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>232200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>193500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>215200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>197500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>202900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>187300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>170000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>168900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>173000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>166900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>171600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>192500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>178800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>172600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>180600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>175500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>149400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>142600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>126400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>123300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>121600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>111900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>129800</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2006600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2062000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2007400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2019100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2081900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2172100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2045700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2149700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2443600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2301200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2460400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3007600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3063800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2956700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2744500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2726000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2548900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2345900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2208500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2138000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1957300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1914000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1898200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1906700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1916900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1848000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1686100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1890200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1805500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1644500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1601700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1598300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1553100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1456100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1445200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1539700</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4563,8 +4668,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4641,228 +4746,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1132100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1147300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1138300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1140000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1153200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1148800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1052400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>980700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>917700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>902600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1274700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1266800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1248300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1201200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1134100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1107400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1084300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1087600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>958600</v>
       </c>
       <c r="W48" s="3">
         <v>958600</v>
       </c>
       <c r="X48" s="3">
+        <v>958600</v>
+      </c>
+      <c r="Y48" s="3">
         <v>966900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>989800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>966200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>978100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>981100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>813400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>776300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>737600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>742800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>740000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>690600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>675600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>665700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>662500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>642900</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3278700</v>
+      </c>
+      <c r="E49" s="3">
         <v>3278100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3289200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3329000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3331000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3343400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3261500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3304200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3332200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2634300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2641500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3922100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3814200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3870000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3848900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3867900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3891200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3900500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3815100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3196400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3199300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3219200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3259100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3271000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3314900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3323700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3327100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3397100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3055700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3069900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3074400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2958200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2925300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2930100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2940800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2948900</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4971,8 +5085,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5081,118 +5198,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E52" s="3">
         <v>112600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>98500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>112000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>121000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>122800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>90500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>111800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>116700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>119500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>116400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>211200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>189300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>168000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>141600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>140800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>148500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>151400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>247500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>226000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>217100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>200000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>144200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>141700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>133500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>136400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>138000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>106100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>98300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>94800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>95300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>102200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>99400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>82200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>80000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5301,118 +5424,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6595700</v>
+      </c>
+      <c r="E54" s="3">
         <v>6584800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6561800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6598400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6673900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6791500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6565000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6618100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6873200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5972700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6120900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8415600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8334100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8243000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7936200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7868800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7696000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7482100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7358700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6519000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6332300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6300100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6291300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6285600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6343400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6289200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5964600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6169700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5697100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5552000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5511400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5349300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5253400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5134100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5128500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5212600</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5451,8 +5580,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5491,136 +5621,140 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>517600</v>
+      </c>
+      <c r="E57" s="3">
         <v>519700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>513900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>493300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>554400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>571400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>568100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>570400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>489500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>423700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>421600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>672600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>756300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>728100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>764900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>735700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>697500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>599200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>620500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>544100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>463900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>426400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>460000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>436500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>476600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>442000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>459000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>437700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>428700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>417100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>428800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>392500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>397000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>378900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>393800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>361900</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>499800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>531100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>499500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>499300</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -5628,28 +5762,28 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>599800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>599500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>599200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>600300</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>400000</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
@@ -5657,8 +5791,8 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -5667,34 +5801,34 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>399900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>399700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>399500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>749300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>350000</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>525000</v>
       </c>
       <c r="AD58" s="3">
         <v>525000</v>
       </c>
       <c r="AE58" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="AF58" s="3">
         <v>350000</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>8</v>
+      <c r="AG58" s="3">
+        <v>350000</v>
       </c>
       <c r="AH58" s="3" t="s">
         <v>8</v>
@@ -5705,454 +5839,469 @@
       <c r="AJ58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK58" s="3">
-        <v>0</v>
+      <c r="AK58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>498600</v>
+      </c>
+      <c r="E59" s="3">
         <v>442400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>57600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>539400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>494300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>491100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>61800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>621700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>551400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>390000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>523900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>775000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>685200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>626700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>806200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>793100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>667200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>597800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>724600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>590900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>488900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>419800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>549600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>540600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>469300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>446800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>508100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>488900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>451800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>373700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>478000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>460000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>394100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>328900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>449000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1016200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1461900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1602300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1532200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1548000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1062500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1200400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1192100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1640700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1413200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1544700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2047900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1441500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1354800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1971100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1528800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1364700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1197000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1345100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1135000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>952800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1246100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1409300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1376600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1695200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1238800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1492100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1451600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1230500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1140800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>906800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>852500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>791100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>707800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>842800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>776700</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2995600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2569600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2295300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2405600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2536000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3185200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2813400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2921400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2757500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2164900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2074300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2786900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3357900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3367900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2309800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2629100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2608300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2682800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2572200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2086500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2245900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2035200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1784600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1949000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1666000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2169700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1809000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1988400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1793300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1538000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1507600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1462200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1391900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1491500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1431100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1585800</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E62" s="3">
         <v>90800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>92300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>85900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>86200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>89200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>99200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>100400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>93600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>102400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>415000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>550700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>582300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>605500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>590500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>656300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>679500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>677900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>665900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>668900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>670500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>660900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>669600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>623300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>637500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>633600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>483500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>496100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>498600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>514900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>495900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>488700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>501700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>504100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>491600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>489900</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6261,8 +6410,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6371,8 +6523,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6481,118 +6636,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4255500</v>
+      </c>
+      <c r="E66" s="3">
         <v>4280200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4139800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4202500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4343300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4510700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4271600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4399100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4696100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3890200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4034000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5385500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5381700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5328200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4871400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4814200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4652500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4557700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4583200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3890400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3870500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3943100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3864700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3950200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3999900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4043700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3786400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3937800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3524000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3195200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2911900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2805000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2686200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2704900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2767000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2853800</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6631,8 +6792,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6741,8 +6903,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6851,8 +7016,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6961,8 +7129,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7071,118 +7242,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3079100</v>
+      </c>
+      <c r="E72" s="3">
         <v>3008600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2956800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2882500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2805500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2701800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2605300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2554200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2475400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2402400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2323800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3277000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3145000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2989400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2807900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2670000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2539300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2358000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2180200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2052700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1954700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1872100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1763000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1692500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1648100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1541400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1448100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1393400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1350500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1249900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1076500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1002000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>892000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>814600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7291,8 +7468,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7401,8 +7581,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7511,118 +7694,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2340200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2304600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2422000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2395900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2330600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2280800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2293400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2219000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2177100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2082500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2086900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3030100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2952400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2914800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3064800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3054600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3043500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2924400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2775500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2628600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2461800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2357000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2426600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2335400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2343500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2245500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2178200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2231900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2173100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2356800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2599500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2544300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2567200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2429200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2361500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2358800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7731,233 +7920,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E81" s="3">
         <v>51400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>105100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>136600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>133900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>96400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>81300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>136500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>102100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>84600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>686700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>204200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>192000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>180900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>772400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>202100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>217200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>177800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>163600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>164600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>115800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>109100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>104100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>105600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>137500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>84700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>85200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>99800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>129600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>75000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>128000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>129500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>137700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>77400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>103600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7996,118 +8194,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E83" s="3">
         <v>28300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>39200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>26600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>21600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>19300</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>31800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>191600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>48600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>46900</v>
       </c>
       <c r="P83" s="3">
         <v>46900</v>
       </c>
       <c r="Q83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="R83" s="3">
         <v>189100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>46200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>47500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>47700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>46600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>39300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>40100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>37500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>40000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>36700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>38200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>37800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>40700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>37500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>37900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>33500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>34000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>32300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>32200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>31800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>33000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8216,8 +8418,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8326,8 +8531,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8436,8 +8644,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8546,8 +8757,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8656,118 +8870,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-83400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>272300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>205300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>261500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-71300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>220200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>332000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>427500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>76100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>566300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>246900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>225000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-183100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>688700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>168100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>331900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-69200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>318900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>246300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>274300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>283400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>241800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>201700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-89700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>260300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>206400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>189200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-51900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>247700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>181400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>189100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>269900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8806,118 +9026,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-29200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-60200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-29700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-64600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-80800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-63500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-69600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-71000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-59500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-54800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-60800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-101200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-47200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-40400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-25400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-84300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-23900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-26900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-49400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-27200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-43600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-39300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9026,8 +9250,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9136,118 +9363,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-44200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-60400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-169800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-80800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-65700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-848700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-42600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-455500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-211800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-54800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-114400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-207100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-47200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-40400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-18500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-799400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-23200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-77000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-49500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-25300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-65900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-496100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-42700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-174500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-50800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-178700</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9286,118 +9519,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E96" s="3">
         <v>30500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>29600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>29800</v>
-      </c>
-      <c r="G96" s="3">
-        <v>30100</v>
       </c>
       <c r="H96" s="3">
         <v>30100</v>
       </c>
       <c r="I96" s="3">
+        <v>30100</v>
+      </c>
+      <c r="J96" s="3">
         <v>29000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>29200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>29100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>29500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-145600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-36200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-36400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-143000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-35900</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-36000</v>
       </c>
       <c r="T96" s="3">
         <v>-36000</v>
       </c>
       <c r="U96" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-33400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-33300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-33100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-33500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-30700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-30600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-30700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-31000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-28100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-28500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-29000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-27400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-27700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-24500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9506,8 +9743,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9616,8 +9856,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9726,334 +9969,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-233300</v>
+      </c>
+      <c r="E100" s="3">
         <v>68000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-180300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-192800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-229000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>238700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-210700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-488400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>567100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-139300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>72500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-176100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>203200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-428600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-115700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-192200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>22800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>420400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-166600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-219500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>77300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-187800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-148900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-182400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>129400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>342600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>16200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-108300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>6000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2200</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-14700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-11100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-14700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-12000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>14400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>9900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>3800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>6400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-105100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-41600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>35500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-63100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-227700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>141600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-103600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>172200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-93600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>51100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>103500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-63200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-45700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>65700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>38600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-28500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>51600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>59500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-127200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>52400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>101100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>45900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>24400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>41900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-40700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-27100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>FBHS</t>
   </si>
@@ -656,517 +656,529 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1077500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1149200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1203300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1033100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1104200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1155300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1240000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1109600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1161300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1261200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1163700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1040000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4723000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1195500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1255400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1140200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4801100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1986300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1936100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1771000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1659700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1652100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1375800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1402700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1470500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1459000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1507200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1327900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1420700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1380800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1429000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1254600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1382500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1348600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1365400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1186800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1301600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1279000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>589000</v>
+      </c>
+      <c r="E9" s="3">
         <v>623400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>659500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>578400</v>
       </c>
-      <c r="G9" s="3">
-        <v>571200</v>
-      </c>
       <c r="H9" s="3">
+        <v>595100</v>
+      </c>
+      <c r="I9" s="3">
         <v>622000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>687000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>622000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>644700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>721100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>695600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>631700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2790100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>716600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>742000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>671800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2840600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1280000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1230300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1126900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1052000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1071500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>892900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>909500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>934600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>934800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>969600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>869100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>920300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>880800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>898900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>814600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>885700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>843200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>850500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>768500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>826400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>798200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>488500</v>
+      </c>
+      <c r="E10" s="3">
         <v>525800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>543800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>454700</v>
       </c>
-      <c r="G10" s="3">
-        <v>533000</v>
-      </c>
       <c r="H10" s="3">
+        <v>509100</v>
+      </c>
+      <c r="I10" s="3">
         <v>533300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>553000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>487600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>516600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>540100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>468100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>408300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1932900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>478900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>513400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>468400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1960500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>706300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>705800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>644100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>607700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>580600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>482900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>493200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>535900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>524200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>537600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>458800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>500400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>500000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>530100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>440000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>496800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>505400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>514900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>418300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>475200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>480800</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,13 +1219,14 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>85400</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1221,11 +1234,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>69900</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1233,11 +1246,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>64600</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1323,8 +1336,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1439,240 +1455,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E14" s="3">
         <v>79600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>27400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>24800</v>
       </c>
-      <c r="G14" s="3">
-        <v>27200</v>
-      </c>
       <c r="H14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I14" s="3">
         <v>10900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>58800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>22200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>32400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>20600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>27000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>7600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>23400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>14000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>23000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>35000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>43400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>38400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>16300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>6100</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>2600</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E15" s="3">
         <v>19400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>17900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>18100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18800</v>
-      </c>
-      <c r="M15" s="3">
-        <v>12600</v>
       </c>
       <c r="N15" s="3">
         <v>12600</v>
       </c>
       <c r="O15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="P15" s="3">
         <v>48300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12500</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>11600</v>
       </c>
       <c r="R15" s="3">
         <v>11600</v>
       </c>
       <c r="S15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="T15" s="3">
         <v>46400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>15900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>16000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>16600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>10900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10500</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>10300</v>
       </c>
       <c r="Z15" s="3">
         <v>10300</v>
       </c>
       <c r="AA15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="AB15" s="3">
         <v>11400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>9900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>10100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>10000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>10800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>8900</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>8200</v>
       </c>
       <c r="AH15" s="3">
         <v>8200</v>
       </c>
       <c r="AI15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>7500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>8000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>8100</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>7700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,240 +1735,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>919300</v>
+      </c>
+      <c r="E17" s="3">
         <v>943900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1004400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>911300</v>
       </c>
-      <c r="G17" s="3">
-        <v>916200</v>
-      </c>
       <c r="H17" s="3">
+        <v>940100</v>
+      </c>
+      <c r="I17" s="3">
         <v>937700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1022900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>951400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>967000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1061000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>988900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>905100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3948700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1002800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1035900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>960400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3990000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1699700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1641200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1522600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1426500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1411900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1202800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1247700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1278000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1291000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1304800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1192300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1280600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1233700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1240400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1219700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1156200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1071900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1095900</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>158200</v>
+      </c>
+      <c r="E18" s="3">
         <v>205300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>198900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>121800</v>
       </c>
-      <c r="G18" s="3">
-        <v>188000</v>
-      </c>
       <c r="H18" s="3">
+        <v>164100</v>
+      </c>
+      <c r="I18" s="3">
         <v>217600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>217100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>158200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>194300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>200200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>174800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>134900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>774300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>192700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>219500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>179800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>811100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>286600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>294900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>248400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>233200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>240200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>173000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>155000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>192500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>168000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>202400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>135600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>140100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>147100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>188600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>119400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>162800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>199500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>209200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>114900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>166400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>183100</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1984,588 +2016,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E20" s="3">
         <v>2400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-7400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>4700</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>17200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>1300</v>
       </c>
       <c r="U20" s="3">
         <v>1300</v>
       </c>
       <c r="V20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W20" s="3">
         <v>-3300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>6100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>9600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E21" s="3">
         <v>222300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>225400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>140800</v>
       </c>
-      <c r="G21" s="3">
-        <v>201200</v>
-      </c>
       <c r="H21" s="3">
+        <v>177300</v>
+      </c>
+      <c r="I21" s="3">
         <v>236700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>237000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>175900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>195200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>228400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>192600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>153800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>977900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>244100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>266600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>228800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>999800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>334100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>343700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>292800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>279700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>281600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>218300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>198600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>201300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>205000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>241300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>174600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>181300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>194200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>229900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>155700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>189300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>234000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>243700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>147500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>197800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>212400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E22" s="3">
         <v>28600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>31200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>30200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>32300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>33300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>27700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>26800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>119200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>33000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>21700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>84300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>22200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>22100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>22400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>24500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>23700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>19000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>17400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>14700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>12900</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>12300</v>
       </c>
       <c r="AK22" s="3">
         <v>12300</v>
       </c>
       <c r="AL22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AM22" s="3">
         <v>11900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>11600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E23" s="3">
         <v>94700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>147700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>69400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>133300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>176500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>170500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>125200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>103900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>172600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>130100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>111300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>667100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>162500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>189200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>160200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>726400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>267300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>275000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>223700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>213600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>222200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>156000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>139000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>138900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>144700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>178600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>113100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>117200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>137700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>174600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>107500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>142400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>189400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>199200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>103800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>153200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E24" s="3">
         <v>23900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>47400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>18000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>39900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>36600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>22600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>36100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>25700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>127200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>21100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>44900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>34000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>166700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>65200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>57800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>45900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>47100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>54000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>37800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>29900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>34900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>39000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>41500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>28600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>28700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>40900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>44900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>27000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>40100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>59800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>58900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>26400</v>
-      </c>
-      <c r="AM24" s="3">
-        <v>48800</v>
       </c>
       <c r="AN24" s="3">
         <v>48800</v>
       </c>
+      <c r="AO24" s="3">
+        <v>48800</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2680,240 +2728,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E26" s="3">
         <v>70800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>100300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>51400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>105100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>136600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>133900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>96400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>81300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>136500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>102100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>85600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>539900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>141400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>144300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>126200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>559700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>202100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>217200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>177800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>166500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>168200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>118200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>109100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>104000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>105700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>137100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>84500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>88500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>96800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>129700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>80500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>102300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>129600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>140300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>77400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>104400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E27" s="3">
         <v>70800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>100300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>51400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>105100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>136600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>133900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>96400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>81300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>136500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>102100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>84600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>539900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>141400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>144300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>126200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>559700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>202100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>217200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>177800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>163600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>164600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>115800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>109100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>104100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>105600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>137500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>84700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>88400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>96700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>129600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>80600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>102300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>129500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>140300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>77400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>104300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3028,8 +3085,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3064,31 +3124,31 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-1000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>146800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>62800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>47700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>54700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>212700</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -3096,14 +3156,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
@@ -3115,37 +3175,40 @@
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>3100</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>25700</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AL29" s="3" t="s">
+      <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-700</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3260,8 +3323,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3376,240 +3442,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>7400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-4700</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-17200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-1300</v>
       </c>
       <c r="U32" s="3">
         <v>-1300</v>
       </c>
       <c r="V32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="W32" s="3">
         <v>3300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>31200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E33" s="3">
         <v>70800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>100300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>51400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>105100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>136600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>133900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>96400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>81300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>136500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>102100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>84600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>686700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>204200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>192000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>180900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>772400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>202100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>217200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>177800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>163600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>164600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>115800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>109100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>104100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>105600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>137500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>84700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>85200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>99800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>129600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>75000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>128000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>129500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>137700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>77400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>103600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3724,245 +3799,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E35" s="3">
         <v>70800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>100300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>51400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>105100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>136600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>133900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>96400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>81300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>136500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>102100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>84600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>686700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>204200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>192000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>180900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>772400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>202100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>217200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>177800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>163600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>164600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>115800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>109100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>104100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>105600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>137500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>84700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>85200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>99800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>129600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>75000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>128000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>129500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>137700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>77400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>103600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4003,8 +4087,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4045,124 +4130,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>264000</v>
+      </c>
+      <c r="E41" s="3">
         <v>223900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>234700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>340000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>381100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>344800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>352600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>359700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>366400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>453400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>681700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>539100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>642500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>345300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>360600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>378200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>471500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>460700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>460000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>356100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>419100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>464500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>398400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>359700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>387900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>336200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>276300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>281200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>262900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>389900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>345500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>244400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>323000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>277100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>252700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>210800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>251500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>278600</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4197,11 +4286,11 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>73000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4277,472 +4366,487 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>513100</v>
+      </c>
+      <c r="E43" s="3">
         <v>565600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>607100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>563700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>514400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>555900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>593600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>615900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>534200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>578600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>621200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>559000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>521800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>936100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>998500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1011600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>885700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>921800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>844600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>828500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>734900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>765200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>657700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>678200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>624800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>640100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>706200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>650100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>571700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>635400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>657500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>631500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>555300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>594700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>595700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>564900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>550700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>568800</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1024900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1041100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1012700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1003500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>960300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>962600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>990500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1025200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>982300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>930000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>954500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>931100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1021300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1502300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1446700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1334700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1193800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1128300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1046800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>958400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>867200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>738300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>732300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>703100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>718600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>758800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>741900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>737900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>678900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>684300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>627000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>619200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>580800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>600100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>581400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>558800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>531100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>562500</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>170800</v>
+      </c>
+      <c r="E45" s="3">
         <v>178300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>150800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>153500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>150300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>153400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>142700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>145400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>135900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>184700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>183900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>196300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>274800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>223900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>258000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>232200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>193500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>215200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>197500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>202900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>187300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>170000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>168900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>173000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>166900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>171600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>192500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>178800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>172600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>180600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>175500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>149400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>142600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>126400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>123300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>121600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>111900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>129800</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1974200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2010200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2006600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2062000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2007400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2019100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2081900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2172100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2045700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2149700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2443600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2301200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2460400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3007600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3063800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2956700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2744500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2726000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2548900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2345900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2208500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2138000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1957300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1914000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1898200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1906700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1916900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1848000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1686100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1890200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1805500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1644500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1601700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1598300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1553100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1456100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1445200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1539700</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4779,8 +4883,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4857,240 +4961,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1065500</v>
+      </c>
+      <c r="E48" s="3">
         <v>1024400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1200400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1132100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1147300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1138300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1140000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1153200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1148800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1052400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>980700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>917700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>902600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1274700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1266800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1248300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1201200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1134100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1107400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1084300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1087600</v>
-      </c>
-      <c r="X48" s="3">
-        <v>958600</v>
       </c>
       <c r="Y48" s="3">
         <v>958600</v>
       </c>
       <c r="Z48" s="3">
+        <v>958600</v>
+      </c>
+      <c r="AA48" s="3">
         <v>966900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>989800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>966200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>978100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>981100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>813400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>776300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>737600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>742800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>740000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>690600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>675600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>665700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>662500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>642900</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3238100</v>
+      </c>
+      <c r="E49" s="3">
         <v>3253300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3278700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3278100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3289200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3329000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3331000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3343400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3261500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3304200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3332200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2634300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2641500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3922100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3814200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3870000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3848900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3867900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3891200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3900500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3815100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3196400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3199300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3219200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3259100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3271000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3314900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3323700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3327100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3397100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3055700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3069900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3074400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2958200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2925300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2930100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2940800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2948900</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5205,8 +5318,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5321,124 +5437,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>222900</v>
+      </c>
+      <c r="E52" s="3">
         <v>230800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>110000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>112600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>98500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>112000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>121000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>122800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>90500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>111800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>116700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>119500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>116400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>211200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>189300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>168000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>141600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>140800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>148500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>151400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>247500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>226000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>217100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>200000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>144200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>141700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>133500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>136400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>138000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>106100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>98300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>94800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>95300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>102200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>99400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>82200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>80000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5553,124 +5675,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6520600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6518700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6595700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6584800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6561800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6598400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6673900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6791500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6565000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6618100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6873200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5972700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6120900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8415600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8334100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8243000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7936200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7868800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7696000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7482100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7358700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6519000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6332300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6300100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6291300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6285600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6343400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6289200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5964600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6169700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5697100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5552000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5511400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5349300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5253400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5134100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5128500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5212600</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5711,8 +5839,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5753,148 +5882,152 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>524600</v>
+      </c>
+      <c r="E57" s="3">
         <v>523200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>517600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>519700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>513900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>493300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>554400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>571400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>568100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>570400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>489500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>423700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>421600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>672600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>756300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>728100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>764900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>735700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>697500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>599200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>620500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>544100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>463900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>426400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>460000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>436500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>476600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>442000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>459000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>437700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>428700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>417100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>428800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>392500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>397000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>378900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>393800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>361900</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>29900</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>499800</v>
       </c>
-      <c r="G58" s="3">
-        <v>531100</v>
-      </c>
       <c r="H58" s="3">
+        <v>499600</v>
+      </c>
+      <c r="I58" s="3">
         <v>499500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>499300</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -5902,28 +6035,28 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>599800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>599500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>599200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>600300</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>400000</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
@@ -5931,8 +6064,8 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -5941,34 +6074,34 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>399900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>399700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>399500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>749300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>350000</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>525000</v>
       </c>
       <c r="AF58" s="3">
         <v>525000</v>
       </c>
       <c r="AG58" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="AH58" s="3">
         <v>350000</v>
       </c>
-      <c r="AI58" s="3" t="s">
-        <v>8</v>
+      <c r="AI58" s="3">
+        <v>350000</v>
       </c>
       <c r="AJ58" s="3" t="s">
         <v>8</v>
@@ -5979,478 +6112,493 @@
       <c r="AL58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM58" s="3">
-        <v>0</v>
+      <c r="AM58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E59" s="3">
         <v>507600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>498600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>442400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>57600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>539400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>494300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>491100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>61800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>621700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>551400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>390000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>523900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>775000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>685200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>626700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>806200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>793100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>667200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>597800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>724600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>590900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>488900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>419800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>549600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>540600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>469300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>446800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>508100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>488900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>451800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>373700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>478000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>460000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>394100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>328900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>449000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1071600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1030800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1016200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1461900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1602300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1532200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1548000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1062500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1192100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1640700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1413200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1544700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2047900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1441500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1354800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1971100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1528800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1364700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1197000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1345100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1135000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>952800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1246100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1409300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1376600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1695200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1238800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1492100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1451600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1230500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1140800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>906800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>852500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>791100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>707800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>842800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>776700</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2788700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2834100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2995600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2569600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2295300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2405600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2536000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3185200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2813400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2921400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2757500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2164900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2074300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2786900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3357900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3367900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2309800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2629100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2608300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2682800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2572200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2086500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2245900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2035200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1784600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1949000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1666000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2169700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1809000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1988400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1793300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1538000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1507600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1462200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1391900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1491500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1431100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1585800</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E62" s="3">
         <v>83700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>84500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>90800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>92300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>85900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>86200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>89200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>99200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>100400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>93600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>102400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>415000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>550700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>582300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>605500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>590500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>656300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>679500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>677900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>665900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>668900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>670500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>660900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>669600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>623300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>637500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>633600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>483500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>496100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>498600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>514900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>495900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>488700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>501700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>504100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>491600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>489900</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6565,8 +6713,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6681,8 +6832,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6797,124 +6951,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4132000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4139700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4255500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4280200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4139800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4202500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4343300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4510700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4271600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4399100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4696100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3890200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4034000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5385500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5381700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5328200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4871400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4814200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4652500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4557700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4583200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3890400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3870500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3943100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3864700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3950200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3999900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4043700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3786400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3937800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3524000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3195200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2911900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2805000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2686200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2704900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2767000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2853800</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6955,8 +7115,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7071,8 +7232,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7187,8 +7351,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7303,8 +7470,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7419,124 +7589,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3135000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3119700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3079100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3008600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2956800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2882500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2805500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2701800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2605300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2554200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2475400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2402400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2323800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3277000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3145000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2989400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2807900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2670000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2539300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2358000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2180200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2052700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1954700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1872100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1763000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1692500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1648100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1541400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1448100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1393400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1350500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1249900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1076500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1002000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>892000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>814600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7651,8 +7827,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7767,8 +7946,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7883,124 +8065,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2388600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2379000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2340200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2304600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2422000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2395900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2330600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2280800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2293400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2219000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2177100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2082500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2086900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3030100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2952400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2914800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3064800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3054600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3043500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2924400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2775500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2628600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2461800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2357000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2426600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2335400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2343500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2245500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2178200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2231900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2173100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2356800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2599500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2544300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2567200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2429200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2361500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2358800</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8115,245 +8303,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46018</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E81" s="3">
         <v>70800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>100300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>51400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>105100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>136600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>133900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>96400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>81300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>136500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>102100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>84600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>686700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>204200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>192000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>180900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>772400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>202100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>217200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>177800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>163600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>164600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>115800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>109100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>104100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>105600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>137500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>84700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>85200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>99800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>129600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>75000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>128000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>129500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>137700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>77400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>103600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8394,124 +8591,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E83" s="3">
         <v>26800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>37100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>28300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>39200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>26600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>21600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>19300</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>31800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>191600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>48600</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>46900</v>
       </c>
       <c r="R83" s="3">
         <v>46900</v>
       </c>
       <c r="S83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="T83" s="3">
         <v>189100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>46200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>47500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>47700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>46600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>39300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>40100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>37500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>40000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>36700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>38200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>37800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>40700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>37500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>37900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>33500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>32300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>32200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>31800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>33000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8626,8 +8827,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8742,8 +8946,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8858,8 +9065,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8974,8 +9184,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9090,124 +9303,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>208200</v>
+      </c>
+      <c r="E89" s="3">
         <v>204400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>149400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-83400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>272300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>205300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>261500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-71300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>220200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>332000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>427500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>76100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>566300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>246900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>225000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-183100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>688700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>168100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>331900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-69200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>318900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>246300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>274300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-13800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>283400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>241800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>201700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-89700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>260300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>206400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>189200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-51900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>247700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>181400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>189100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>269900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9248,124 +9467,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-29200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-60200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-29700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-38800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-64600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-80800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-63500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-69600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-71000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-59500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-54800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-60800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-101200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-47200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-40400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-25400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-84300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-23900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-49400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-27200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-43600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-39300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9480,8 +9703,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9596,124 +9822,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-20500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-44200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-28500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-60400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-169800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-80800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-65700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-848700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-42600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-455500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-211800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-54800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-114400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-207100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-47200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-40400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-18500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-799400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-23900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-23200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-77000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-49500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-25300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-65900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-496100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-42700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-174500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-50800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-178700</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9754,8 +9986,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9763,115 +9996,118 @@
         <v>30000</v>
       </c>
       <c r="E96" s="3">
+        <v>30000</v>
+      </c>
+      <c r="F96" s="3">
         <v>30100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>30500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>29600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>29800</v>
-      </c>
-      <c r="I96" s="3">
-        <v>30100</v>
       </c>
       <c r="J96" s="3">
         <v>30100</v>
       </c>
       <c r="K96" s="3">
+        <v>30100</v>
+      </c>
+      <c r="L96" s="3">
         <v>29000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>29200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>29100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>29500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-145600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-36400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-37200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-143000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-35900</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-36000</v>
       </c>
       <c r="V96" s="3">
         <v>-36000</v>
       </c>
       <c r="W96" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="X96" s="3">
         <v>-33400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-33300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-33100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-33500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-30700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-30600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-30700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-31000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-28100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-28500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-29000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-27400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-27700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-24500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9986,8 +10222,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10102,8 +10341,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10218,352 +10460,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-150700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-187300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-233300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>68000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-180300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-192800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-229000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>238700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-210700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-488400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>567100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-139300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>72500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-176100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>203200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-428600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-115700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-192200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>22800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>420400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-166600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-219500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>77300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-187800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-148900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-182400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>129400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>342600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>16200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-108300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>6000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E101" s="3">
         <v>8500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2200</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-14700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-12000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-12000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>14400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>9900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2500</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-105100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-41600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>35500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-30600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-63100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-227700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>141600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-103600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>172200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-93600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>51100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>103500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-63200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-45700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>65700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>38600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-28500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>51600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>59500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>18200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-127200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>52400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>101100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>45900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>24400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>41900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-40700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-27100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FBIN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
     <t>FBHS</t>
   </si>
@@ -656,529 +656,542 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E7" s="2">
         <v>46018</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45654</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45290</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1011300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1077500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1149200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1203300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1033100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1104200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1155300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1240000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1109600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1161300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1261200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1163700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1040000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4723000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1195500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1255400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1140200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4801100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1986300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1936100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1771000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1659700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1652100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1375800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1402700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1470500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1459000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1507200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1327900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1420700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1380800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1429000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1254600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1382500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1348600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1365400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1186800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1301600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1279000</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>574700</v>
+      </c>
+      <c r="E9" s="3">
         <v>589000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>623400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>659500</v>
       </c>
-      <c r="G9" s="3">
-        <v>578400</v>
-      </c>
       <c r="H9" s="3">
+        <v>569100</v>
+      </c>
+      <c r="I9" s="3">
         <v>595100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>622000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>687000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>622000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>644700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>721100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>695600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>631700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2790100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>716600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>742000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>671800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2840600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1280000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1230300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1126900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1052000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1071500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>892900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>909500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>934600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>934800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>969600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>869100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>920300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>880800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>898900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>814600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>885700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>843200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>850500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>768500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>826400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>798200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>436600</v>
+      </c>
+      <c r="E10" s="3">
         <v>488500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>525800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>543800</v>
       </c>
-      <c r="G10" s="3">
-        <v>454700</v>
-      </c>
       <c r="H10" s="3">
+        <v>464000</v>
+      </c>
+      <c r="I10" s="3">
         <v>509100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>533300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>553000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>487600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>516600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>540100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>468100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>408300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1932900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>478900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>513400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>468400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1960500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>706300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>705800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>644100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>607700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>580600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>482900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>493200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>535900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>524200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>537600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>458800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>500400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>500000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>530100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>440000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>496800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>505400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>514900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>418300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>475200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>480800</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1220,16 +1233,17 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>85400</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1237,11 +1251,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>69900</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1249,11 +1263,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>64600</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1339,8 +1353,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1458,246 +1475,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="3">
         <v>36700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>79600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>27400</v>
       </c>
-      <c r="G14" s="3">
-        <v>24800</v>
-      </c>
       <c r="H14" s="3">
+        <v>38800</v>
+      </c>
+      <c r="I14" s="3">
         <v>3300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>15900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>58800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>22200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>32400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>20600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>27000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>3600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>7600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>23400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>14000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>23000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>35000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>43400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>38400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>16300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>18100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>6100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>2600</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E15" s="3">
         <v>18800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>18300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>18100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>18800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>12600</v>
       </c>
       <c r="O15" s="3">
         <v>12600</v>
       </c>
       <c r="P15" s="3">
+        <v>12600</v>
+      </c>
+      <c r="Q15" s="3">
         <v>48300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12500</v>
-      </c>
-      <c r="R15" s="3">
-        <v>11600</v>
       </c>
       <c r="S15" s="3">
         <v>11600</v>
       </c>
       <c r="T15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="U15" s="3">
         <v>46400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>15900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>16000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>16600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>10500</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>10300</v>
       </c>
       <c r="AA15" s="3">
         <v>10300</v>
       </c>
       <c r="AB15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="AC15" s="3">
         <v>11400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>9900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>10100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>10000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>10800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>8900</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>8200</v>
       </c>
       <c r="AI15" s="3">
         <v>8200</v>
       </c>
       <c r="AJ15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AK15" s="3">
         <v>8100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>7500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>8000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>8100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>7700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,246 +1762,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>945100</v>
+      </c>
+      <c r="E17" s="3">
         <v>919300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>943900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1004400</v>
       </c>
-      <c r="G17" s="3">
-        <v>911300</v>
-      </c>
       <c r="H17" s="3">
+        <v>897300</v>
+      </c>
+      <c r="I17" s="3">
         <v>940100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>937700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1022900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>951400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>967000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1061000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>988900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>905100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3948700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1002800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1035900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>960400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3990000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1699700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1641200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1522600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1426500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1411900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1202800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1247700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1278000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1291000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1304800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1192300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1280600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1233700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1240400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1219700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1149100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1156200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1071900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1135200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1095900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E18" s="3">
         <v>158200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>205300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>198900</v>
       </c>
-      <c r="G18" s="3">
-        <v>121800</v>
-      </c>
       <c r="H18" s="3">
+        <v>135800</v>
+      </c>
+      <c r="I18" s="3">
         <v>164100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>217600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>217100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>158200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>194300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>174800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>134900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>774300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>192700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>219500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>179800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>811100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>286600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>294900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>248400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>233200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>240200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>173000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>155000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>192500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>168000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>202400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>135600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>140100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>147100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>188600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>119400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>162800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>199500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>209200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>114900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>166400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>183100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2017,603 +2050,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>8000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4700</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>17200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>1300</v>
       </c>
       <c r="V20" s="3">
         <v>1300</v>
       </c>
       <c r="W20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X20" s="3">
         <v>-3300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>9600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>2300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E21" s="3">
         <v>169000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>222300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>225400</v>
       </c>
-      <c r="G21" s="3">
-        <v>140800</v>
-      </c>
       <c r="H21" s="3">
+        <v>154800</v>
+      </c>
+      <c r="I21" s="3">
         <v>177300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>236700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>237000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>175900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>195200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>228400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>192600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>153800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>977900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>244100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>266600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>228800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>999800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>334100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>343700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>292800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>279700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>281600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>218300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>198600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>201300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>205000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>241300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>174600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>181300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>194200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>229900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>155700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>189300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>234000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>243700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>147500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>197800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>212400</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E22" s="3">
         <v>26800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>31200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>28600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>30200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>32300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>30100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>28600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>33300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>27700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>26800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>119200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>33000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>30500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>84300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>22200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>22100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>22400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>23600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>19000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>17400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>14700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>12900</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>12300</v>
       </c>
       <c r="AL22" s="3">
         <v>12300</v>
       </c>
       <c r="AM22" s="3">
+        <v>12300</v>
+      </c>
+      <c r="AN22" s="3">
         <v>11900</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>11600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E23" s="3">
         <v>93200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>94700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>147700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>69400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>133300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>176500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>170500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>125200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>103900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>172600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>130100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>111300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>667100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>162500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>189200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>160200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>726400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>267300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>275000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>223700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>213600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>222200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>156000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>139000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>138900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>144700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>178600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>113100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>117200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>137700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>174600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>107500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>142400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>189400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>199200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>103800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>153200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E24" s="3">
         <v>16800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>23900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>47400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>36600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>22600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>36100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>25700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>127200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>21100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>44900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>34000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>166700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>65200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>57800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>45900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>47100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>54000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>37800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>29900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>34900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>39000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>41500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>28600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>28700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>40900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>44900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>27000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>40100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>59800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>58900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>26400</v>
-      </c>
-      <c r="AN24" s="3">
-        <v>48800</v>
       </c>
       <c r="AO24" s="3">
         <v>48800</v>
       </c>
+      <c r="AP24" s="3">
+        <v>48800</v>
+      </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2731,246 +2780,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E26" s="3">
         <v>76400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>70800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>100300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>51400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>105100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>136600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>133900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>96400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>81300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>136500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>102100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>85600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>539900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>141400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>144300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>126200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>559700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>202100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>217200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>177800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>166500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>168200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>118200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>109100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>104000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>105700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>137100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>84500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>88500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>96800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>129700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>80500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>102300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>129600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>140300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>77400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>104400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E27" s="3">
         <v>76400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>70800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>100300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>51400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>105100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>136600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>133900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>96400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>81300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>136500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>102100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>84600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>539900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>141400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>144300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>126200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>559700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>202100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>217200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>177800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>163600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>164600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>115800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>109100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>104100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>105600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>137500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>84700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>88400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>96700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>129600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>80600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>102300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>129500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>140300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>77400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>104300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>121900</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3088,8 +3146,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3127,31 +3188,31 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-1000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>146800</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>62800</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>47700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>54700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>212700</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
@@ -3159,14 +3220,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -3178,37 +3239,40 @@
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>3100</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>25700</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
       <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AM29" s="3" t="s">
+      <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-700</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3326,8 +3390,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3445,246 +3512,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4700</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-17200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-1300</v>
       </c>
       <c r="V32" s="3">
         <v>-1300</v>
       </c>
       <c r="W32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="X32" s="3">
         <v>3300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>31200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-9600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>7500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E33" s="3">
         <v>76400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>70800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>100300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>51400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>105100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>136600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>133900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>96400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>81300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>136500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>102100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>84600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>686700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>204200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>192000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>180900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>772400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>202100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>217200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>177800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>163600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>164600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>115800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>109100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>104100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>105600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>137500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>84700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>85200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>99800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>129600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>128000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>129500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>137700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>77400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>103600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3802,251 +3878,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E35" s="3">
         <v>76400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>70800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>100300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>51400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>105100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>136600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>133900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>96400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>81300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>136500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>102100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>84600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>686700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>204200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>192000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>180900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>772400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>202100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>217200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>177800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>163600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>164600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>115800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>109100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>104100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>105600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>137500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>84700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>85200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>99800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>129600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>128000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>129500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>137700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>77400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>103600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E38" s="2">
         <v>46018</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45654</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45290</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4088,8 +4173,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4131,127 +4217,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>223100</v>
+      </c>
+      <c r="E41" s="3">
         <v>264000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>223900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>234700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>340000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>381100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>344800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>352600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>359700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>366400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>453400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>681700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>539100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>642500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>345300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>360600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>378200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>471500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>460700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>460000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>356100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>419100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>464500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>398400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>359700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>387900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>336200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>276300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>281200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>262900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>389900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>345500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>244400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>323000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>277100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>252700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>210800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>251500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>278600</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4289,11 +4379,11 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>73000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4369,484 +4459,499 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>584700</v>
+      </c>
+      <c r="E43" s="3">
         <v>513100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>565600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>607100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>563700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>514400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>555900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>593600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>615900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>534200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>578600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>621200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>559000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>521800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>936100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>998500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1011600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>885700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>921800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>844600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>828500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>734900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>765200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>657700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>678200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>624800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>640100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>706200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>650100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>571700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>635400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>657500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>631500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>555300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>594700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>595700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>564900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>550700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>568800</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1038100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1024900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1041100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1012700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1003500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>960300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>962600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>990500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1025200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>982300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>930000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>954500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>931100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1021300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1502300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1446700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1334700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1193800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1128300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1046800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>958400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>867200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>738300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>732300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>703100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>718600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>758800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>741900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>737900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>678900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>684300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>627000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>619200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>580800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>600100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>581400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>558800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>531100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>562500</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>176400</v>
+      </c>
+      <c r="E45" s="3">
         <v>170800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>178300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>150800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>153500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>150300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>153400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>142700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>145400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>135900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>184700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>183900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>196300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>274800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>223900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>258000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>232200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>193500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>215200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>197500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>202900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>187300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>170000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>168900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>173000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>166900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>171600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>192500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>178800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>172600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>180600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>175500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>149400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>142600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>126400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>123300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>121600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>111900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>129800</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2023700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1974200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2010200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2006600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2062000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2007400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2019100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2081900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2172100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2045700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2149700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2443600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2301200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2460400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3007600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3063800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2956700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2744500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2726000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2548900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2345900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2208500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2138000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1957300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1914000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1898200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1906700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1916900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1848000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1686100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1890200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1805500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1644500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1601700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1598300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1553100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1456100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1445200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1539700</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4886,8 +4991,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4964,246 +5069,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1064800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1065500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1024400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1200400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1132100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1147300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1138300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1140000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1153200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1148800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1052400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>980700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>917700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>902600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1274700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1266800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1248300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1201200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1134100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1107400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1084300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1087600</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>958600</v>
       </c>
       <c r="Z48" s="3">
         <v>958600</v>
       </c>
       <c r="AA48" s="3">
+        <v>958600</v>
+      </c>
+      <c r="AB48" s="3">
         <v>966900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>989800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>966200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>978100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>981100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>813400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>776300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>737600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>742800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>740000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>690600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>675600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>665700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>662500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>642900</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3214100</v>
+      </c>
+      <c r="E49" s="3">
         <v>3238100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3253300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3278700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3278100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3289200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3329000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3331000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3343400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3261500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3304200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3332200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2634300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2641500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3922100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3814200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3870000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3848900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3867900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3891200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3900500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3815100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3196400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3199300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3219200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3259100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3271000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3314900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3323700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3327100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3397100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3055700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3069900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3074400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2958200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2925300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2930100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2940800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2948900</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5321,8 +5435,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5440,127 +5557,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>243200</v>
+      </c>
+      <c r="E52" s="3">
         <v>222900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>230800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>110000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>112600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>98500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>112000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>121000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>122800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>90500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>111800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>116700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>119500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>116400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>211200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>189300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>168000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>141600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>140800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>148500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>151400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>247500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>226000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>217100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>200000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>144200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>141700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>133500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>136400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>138000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>106100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>98300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>94800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>95300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>102200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>99400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>82200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>80000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>81100</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5678,127 +5801,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6545800</v>
+      </c>
+      <c r="E54" s="3">
         <v>6520600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6518700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6595700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6584800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6561800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6598400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6673900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6791500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6565000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6618100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6873200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5972700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6120900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8415600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8334100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8243000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7936200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7868800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7696000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7482100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7358700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6519000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6332300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6300100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6291300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6285600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6343400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6289200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5964600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6169700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5697100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5552000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5511400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5349300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5253400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5134100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5128500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>5212600</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5840,8 +5969,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5883,154 +6013,158 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>507300</v>
+      </c>
+      <c r="E57" s="3">
         <v>524600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>523200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>517600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>519700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>513900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>493300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>554400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>571400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>568100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>570400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>489500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>423700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>421600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>672600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>756300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>728100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>764900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>735700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>697500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>599200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>620500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>544100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>463900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>426400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>460000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>436500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>476600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>442000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>459000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>437700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>428700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>417100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>428800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>392500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>397000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>378900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>393800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>361900</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>29900</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>499800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>499600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>499500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>499300</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -6038,28 +6172,28 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>599800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>599500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>599200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>600300</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>400000</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
@@ -6067,8 +6201,8 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -6077,34 +6211,34 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>399900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>399700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>399500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>749300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>350000</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>525000</v>
       </c>
       <c r="AG58" s="3">
         <v>525000</v>
       </c>
       <c r="AH58" s="3">
-        <v>350000</v>
+        <v>525000</v>
       </c>
       <c r="AI58" s="3">
         <v>350000</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>8</v>
+      <c r="AJ58" s="3">
+        <v>350000</v>
       </c>
       <c r="AK58" s="3" t="s">
         <v>8</v>
@@ -6115,490 +6249,505 @@
       <c r="AM58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN58" s="3">
-        <v>0</v>
+      <c r="AN58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>441700</v>
+      </c>
+      <c r="E59" s="3">
         <v>56600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>507600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>498600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>442400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>57600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>539400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>494300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>491100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>61800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>621700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>551400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>390000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>523900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>775000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>685200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>626700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>806200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>793100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>667200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>597800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>724600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>590900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>488900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>419800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>549600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>540600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>469300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>446800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>508100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>488900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>451800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>373700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>478000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>460000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>394100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>328900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>449000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>414800</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>949000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1071600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1030800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1016200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1461900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1602300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1532200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1548000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1062500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1200400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1192100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1640700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1413200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1544700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2047900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1441500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1354800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1971100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1528800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1364700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1197000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1345100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1135000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>952800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1246100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1409300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1376600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1695200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1238800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1492100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1451600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1230500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1140800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>906800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>852500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>791100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>707800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>842800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>776700</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2962900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2788700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2834100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2995600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2569600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2295300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2405600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2536000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3185200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2813400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2921400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2757500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2164900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2074300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2786900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3357900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3367900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2309800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2629100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2608300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2682800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2572200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2086500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2245900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2035200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1784600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1949000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1666000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2169700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1809000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1988400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1793300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1538000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1507600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1462200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1391900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1491500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1431100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1585800</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E62" s="3">
         <v>101600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>83700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>84500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>90800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>92300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>85900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>86200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>89200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>99200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>100400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>93600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>102400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>415000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>550700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>582300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>605500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>590500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>656300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>679500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>677900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>665900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>668900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>670500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>660900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>669600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>623300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>637500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>633600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>483500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>496100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>498600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>514900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>495900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>488700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>501700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>504100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>491600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>489900</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6716,8 +6865,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6835,8 +6987,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6954,127 +7109,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4188900</v>
+      </c>
+      <c r="E66" s="3">
         <v>4132000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4139700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4255500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4280200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4139800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4202500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4343300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4510700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4271600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4399100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4696100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3890200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4034000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5385500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5381700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5328200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4871400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4814200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4652500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4557700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4583200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3890400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3870500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3943100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3864700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3950200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3999900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4043700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3786400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3937800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3524000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3195200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2911900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2805000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2686200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2704900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2767000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2853800</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7116,8 +7277,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7235,8 +7397,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7354,8 +7519,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7473,8 +7641,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7592,127 +7763,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3159200</v>
+      </c>
+      <c r="E72" s="3">
         <v>3135000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3119700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3079100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3008600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2956800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2882500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2805500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2701800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2605300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2554200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2475400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2402400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2323800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3277000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3145000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2989400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2807900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2670000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2539300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2358000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2180200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2052700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1954700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1872100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1763000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1692500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1648100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1541400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1448100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1393400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1350500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1249900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1076500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1002000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>892000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>814600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>738400</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7830,8 +8007,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7949,8 +8129,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8068,127 +8251,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2356900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2388600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2379000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2340200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2304600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2422000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2395900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2330600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2280800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2293400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2219000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2177100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2082500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2086900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3030100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2952400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2914800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3064800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3054600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3043500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2924400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2775500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2628600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2461800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2357000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2426600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2335400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2343500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2245500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2178200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2231900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2173100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2356800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2599500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2544300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2567200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2429200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2361500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2358800</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8306,251 +8495,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46109</v>
+      </c>
+      <c r="E80" s="2">
         <v>46018</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45654</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45290</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E81" s="3">
         <v>76400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>70800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>100300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>51400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>105100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>136600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>133900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>96400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>81300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>136500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>102100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>84600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>686700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>204200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>192000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>180900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>772400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>202100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>217200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>177800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>163600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>164600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>115800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>109100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>104100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>105600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>137500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>84700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>85200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>99800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>129600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>75000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>128000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>129500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>137700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>77400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>103600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>123400</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8592,127 +8790,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E83" s="3">
         <v>28300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>37100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>28300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>39200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>19300</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>191600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>48600</v>
-      </c>
-      <c r="R83" s="3">
-        <v>46900</v>
       </c>
       <c r="S83" s="3">
         <v>46900</v>
       </c>
       <c r="T83" s="3">
+        <v>46900</v>
+      </c>
+      <c r="U83" s="3">
         <v>189100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>46200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>47500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>47700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>46600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>39300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>40100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>37500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>40000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>36700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>38200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>37800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>40700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>37500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>37900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>33500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>34000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>32300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>32200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>31800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>33000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>29900</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8830,8 +9032,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8949,8 +9154,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9068,8 +9276,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9187,8 +9398,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9306,127 +9520,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-119200</v>
+      </c>
+      <c r="E89" s="3">
         <v>208200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>204400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>149400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-83400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>272300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>205300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>261500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-71300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>220200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>332000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>427500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>76100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>566300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>246900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>225000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-183100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>688700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>168100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>331900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-69200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>318900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>246300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>274300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-13800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>283400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>241800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>201700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-89700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>260300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>206400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>189200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-51900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>247700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>181400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>189100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>269900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>215600</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9468,127 +9688,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-29200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-60200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-29700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-38800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-64600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-80800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-63500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-69600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-71000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-59500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-54800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-60800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-101200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-47200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-40400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-25400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-84300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-23900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-49400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-27500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-27700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-27200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-43600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-39300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-36000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-31400</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9706,8 +9930,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9825,127 +10052,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-20500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-44200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-60400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-169800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-80800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-65700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-848700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-42600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-455500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-211800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-54800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-114400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-207100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-47200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-40400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-18500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-799400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-23900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-77000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-49500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-25500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-25300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-65900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-496100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-42700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-174500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-55100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-28500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-29600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-50800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-178700</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9987,127 +10220,131 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>30000</v>
+        <v>31200</v>
       </c>
       <c r="E96" s="3">
         <v>30000</v>
       </c>
       <c r="F96" s="3">
+        <v>30000</v>
+      </c>
+      <c r="G96" s="3">
         <v>30100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>30500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>29600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>29800</v>
-      </c>
-      <c r="J96" s="3">
-        <v>30100</v>
       </c>
       <c r="K96" s="3">
         <v>30100</v>
       </c>
       <c r="L96" s="3">
+        <v>30100</v>
+      </c>
+      <c r="M96" s="3">
         <v>29000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>29200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>29100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>29500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-145600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-36200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-36400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-37200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-143000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-35900</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-36000</v>
       </c>
       <c r="W96" s="3">
         <v>-36000</v>
       </c>
       <c r="X96" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-33400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-33300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-33100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-33500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-30700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-30600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-30700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-31000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-28100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-28500</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-29000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-29600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-27400</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-27700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-27600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-24500</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-24700</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10225,8 +10462,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10344,8 +10584,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10463,361 +10706,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-150700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-187300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-233300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>68000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-180300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-192800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-229000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>238700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-210700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-488400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>567100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-139300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>72500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-36000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-176100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>203200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-428600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-115700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-192200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>22800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>420400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-166600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>77300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-187800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-148900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-182400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>129400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-314200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>342600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-51400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>16200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-26600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-108300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-121200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>6000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-240900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-35700</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>8200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2200</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-14700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-12000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-14700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-12000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>14400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>9900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-7400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>6400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2500</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E102" s="3">
         <v>39900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-105100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-41600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>35500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-30600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-63100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-227700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>141600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-103600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>172200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-15600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-93600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>51100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>103500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-63200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-45700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>65700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>38600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-28500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>51600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>59500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>18200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-127200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>52400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>101100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-78600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>45900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>24400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>41900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-40700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-27100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-100</v>
       </c>
     </row>
